--- a/output/第10期計画_第9期評価のレッドチームレビュー.xlsx
+++ b/output/第10期計画_第9期評価のレッドチームレビュー.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_想定される反論と応答" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_反証条件と検証計画" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_対応方針" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_対応の実施結果" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4178,4 +4179,758 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>対応の実施結果（令和8年7月29日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="56" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>追加のデータなしで対応できる指摘について、各成果物への反映を実施した。実施内容と反映先を記録する。資料の受領を要する指摘は、確認事項として発注者に依頼した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>重大度</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>指摘の要旨</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>対応状況</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>実施した内容</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>反映先</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="76" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>年齢調整が不十分</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>妥当性検証 所見7に留意を追記し、65〜74歳の認定率と5歳階級別の年齢調整を行っていないこと、W144が悪化していることと方向が異なることを明記した。整合の実証は確認事項No.37の資料を待つ。</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>妥当性検証 01シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="76" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>交付金の得点が第8期の評価</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>所見18の表題に「令和5年調査＝第8期の取組を反映」を追記し、留意として評価対象が主に令和4年度の実施状況であることを明記した。保険料と施策評価の他団体比較04シートの副題にも同旨を追記した。</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>妥当性検証 01シート
+保険料と施策評価の他団体比較 04シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="76" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>剰余42百万円が概算</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>所見9に「剰余の額は概算である」旨と、令和6年度が年度換算値であること、決算で確定値に置き換えることを明記した。</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>妥当性検証 01シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="76" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>第7期基準額の訂正が未確認</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>対応済（確認待ち）</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>保険料と施策評価の他団体比較02シートに訂正の経緯と条例による確認を要する旨を注記済み。確認事項No.32として依頼した。</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>保険料と施策評価の他団体比較 02シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="76" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>3町の数値目標の判定が検索語依存</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>訂正（指摘的中）</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>3町の計画を各章にわたり目視で再点検した結果、東川町は令和6〜8年度を対象とする事業の数値目標を6事業10項目以上設定していることが判明した（訪問型サービス200人／年、通所型サービス150人／年、介護予防ケアマネジメント720件／年、介護予防把握200件／年、いきいきセンター開所200日・登録80名、地域まるごと元気アップ48回・25人）。美瑛町・東神楽町は事業の数値目標を設定していない。東神楽町の令和6〜8年度の数表は人口・認定者数の推計値であり目標値ではない。所見5を「数値目標を設定しているのは東川町のみ」に全面的に改めた。</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>妥当性検証 01・09・12シート
+素案 第1章第2節・資料2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="76" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>軽微</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>年度表記が紛らわしい</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>所見7の根拠に「令和8年3月末（令和7年度末）」と年度を明記し、第9期の最終年度の実績が令和9年3月末に確定することを追記した。</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>妥当性検証 01シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="76" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>給付水準の要因が特定できていない</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>所見1の表題を「受給率と受給者単価に由来する」に改め、3要素が独立でないこと、区域外施設の利用の可能性、自給率の算定により検証することを留意として追記した。素案の該当箇所も同旨に改めた。</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>妥当性検証 01シート
+素案 第2章第2節</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="76" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>利用率低下と供給制約の結びつけに飛躍</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>所見2の対応欄に、事実だけでは供給制約は導けないこと、認定申請の勧奨によるものであれば施策の方向が逆になること、要因を特定するまで断定しないことを明記した。素案の該当箇所を「要因の分解が中心論点であり、現時点でいずれかに特定していません」に改めた。</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>妥当性検証 01シート
+素案 第2章第2節3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="76" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>「全国トップ級」が過大</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>所見19の表題を「令和6年度分指標では成果が全国を上回る」に改め、成果指標の統計的な安定性が未検証であること、「全国トップ級」等の表現を用いないことを明記した。保険料と施策評価の他団体比較04・05シートにも同旨を追記した。</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>妥当性検証 01シート
+保険料と施策評価の他団体比較 04・05シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="76" customHeight="1">
+      <c r="A14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>「在宅化」が政策の成果と誤読される</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>所見3に、施設定員の縮小と同時に進んでおり在宅の支援体制が整った結果ではないこと、家族介護への転嫁の可能性が高いことを追記した。素案の見出しを「重度者の在宅・居住系割合の上昇」に改め、本文も同旨に改めた。</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>妥当性検証 01シート
+素案 第2章第3節</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="76" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>評価可能性の判定が机上評価</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>施策体系新旧対照表の列名を「計画記載上の評価可能性」に改め、計画の記載の判定であって施策の良否ではないこと、事業が実施され成果を上げている可能性を排除していないことを注記した。</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>施策体系新旧対照表 施策の新旧対照</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="76" customHeight="1">
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>人口推計の乖離を片側から評価</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>未対応（資料待ち）</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>令和6年・令和7年の住民基本台帳実績を両推計に当てはめる検証には町別人口の実績を要する（確認事項No.11）。</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="76" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>評価範囲の誇張</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>妥当性検証01シートの表題を「主要所見20件（中間・記載事項の検証）」に改め、副題にプロセス評価を行っていないこと、現時点の評価が中間評価であることを明記した。素案第3章の冒頭に評価の範囲を示す文を新設した。業務工程管理表の(2)の進捗を0.80から0.65に改めた。</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>妥当性検証 01シート
+素案 第3章
+業務工程管理表 01シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="76" customHeight="1">
+      <c r="A18" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>比較対象の選定が事後的</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>妥当性検証01シートの副題、調査クロス集計・分析19・21シートの副題、保険料と施策評価の他団体比較の該当箇所に、比較対象が入手可能なものであり暫定的であることを明記した。</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>妥当性検証 01シート
+調査クロス集計・分析 19・21シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="76" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>保険者の自己評価との関係が未整理</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>未対応（資料待ち）</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>第9期の自己評価の有無と内容の確認を要する（確認事項No.7）。存在する場合は本評価との対照表を作成する。</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="76" customHeight="1">
+      <c r="A20" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>小規模保険者の制約を考慮しない比較</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>妥当性検証01シートの副題及び保険料と施策評価の他団体比較04シートの副題に、評価項目に職員体制や実施件数を問うものが含まれ、人口規模を揃えた比較になっていないことを明記した。</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>妥当性検証 01シート
+保険料と施策評価の他団体比較 04シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="76" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>軽微</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>判定基準が資料により異なる</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>妥当性検証01シートの副題に判定の閾値を明記し、調査クロス集計・分析19シートの注に、1.0ポイントの閾値が本表独自のものであることを明記した。</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>妥当性検証 01シート
+調査クロス集計・分析 19シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="76" customHeight="1">
+      <c r="A22" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>反証条件が示されていない</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>本表06シートに主要所見12件の反証条件と検証計画を作成した。第10期の年次PDCAの手順に位置づける。</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>本表 06シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>【対応状況の集計】</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>記述の修正・表現の限定・注記の追加を実施した</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="8" t="n"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>訂正（指摘的中）</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>No.5。3町の数値目標に関する判定が誤りであったため全面的に改めた</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="8" t="n"/>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>No.1。留意の追記までを行い、実証は資料の受領後</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="8" t="n"/>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>対応済（確認待ち）</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>No.4。注記済みで、条例による確認を依頼済み</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="8" t="n"/>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>未対応（資料待ち）</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>No.12・No.15。いずれも確認事項として依頼済み</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="8" t="n"/>
+    </row>
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>注1）No.5は本レビューの指摘が的中し、評価の結論そのものを訂正した事例である。「3町の高齢者福祉計画に数値目標が1件も設定されていない」という所見は誤りであり、東川町は令和6〜8年度を対象とする事業の数値目標を6事業10項目以上設定していた。検索語に依存した判定の危うさが実証された。注2）この訂正は第10期にとって前向きな材料でもある。東川町には事業の数値目標を年度別に設定し実績と対比する仕組みが既にあるため、第10期の共通指標の掲載は同町では実現可能性が高く、美瑛町・東神楽町にはその様式を参考として示すことができる。注3）残る未対応2件（No.12・No.15）と一部対応1件（No.1）は、いずれも資料の受領を要する。確認事項No.7・No.11・No.37として依頼済みである。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/第10期計画_第9期評価のレッドチームレビュー.xlsx
+++ b/output/第10期計画_第9期評価のレッドチームレビュー.xlsx
@@ -4187,7 +4187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4260,17 +4260,20 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>一部対応</t>
+          <t>訂正（指摘的中）</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>妥当性検証 所見7に留意を追記し、65〜74歳の認定率と5歳階級別の年齢調整を行っていないこと、W144が悪化していることと方向が異なることを明記した。整合の実証は確認事項No.37の資料を待つ。</t>
+          <t>見える化B4a・B4c・B4d・B4e・B5a・B6a・B6bを受領し、認定率の年齢調整分析（7シート）を作成した。①65〜74歳の認定率は平成30年3.78％から令和8年4.03％へ上昇しており、「全年齢層で低下」は成り立たない。②3階級による直接法では、粗率が令和元年20.30％から令和8年21.80％へ＋1.50ポイント上昇する一方、年齢調整済みは20.33％から19.69％へ▲0.64ポイント低下する。見える化の調整済み認定率（17.8％→16.7％）とも方向が一致し、所見7の結論そのものは裏付けられた。③一方、従来の説明「軽度は改善・中重度は悪化」は誤りであった。重度（要介護3〜5）は5.4％から4.7％へ低下が続き、軽度（要支援1〜要介護2）は令和5年11.7％を底に令和7年12.0％へ上昇に転じている。④W144とB5aは基準人口・調整方法・時点・単位が異なるため直接比較できないことを整理し、従来の説明を撤回した。</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>妥当性検証 01シート</t>
+          <t>認定率の年齢調整分析（新規7シート）
+妥当性検証 01シート
+素案 第2章第2節・第3章第4節
+保険料と施策評価の他団体比較 05・06シート</t>
         </is>
       </c>
     </row>
@@ -4847,11 +4850,11 @@
         </is>
       </c>
       <c r="B27" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>No.5。3町の数値目標に関する判定が誤りであったため全面的に改めた</t>
+          <t>No.5（3町の数値目標）とNo.1（年齢調整）。いずれも指摘が的中し、評価の記述を訂正した。特にNo.1では「軽度は改善・中重度は悪化」という従来の説明が逆であることが判明し、施策の重点に影響する</t>
         </is>
       </c>
       <c r="D27" s="7" t="n"/>
@@ -4861,7 +4864,7 @@
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>一部対応</t>
+          <t>対応済（確認待ち）</t>
         </is>
       </c>
       <c r="B28" s="16" t="n">
@@ -4869,7 +4872,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>No.1。留意の追記までを行い、実証は資料の受領後</t>
+          <t>No.4。注記済みで、条例による確認を依頼済み</t>
         </is>
       </c>
       <c r="D28" s="7" t="n"/>
@@ -4879,55 +4882,36 @@
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>対応済（確認待ち）</t>
+          <t>未対応（資料待ち）</t>
         </is>
       </c>
       <c r="B29" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>No.4。注記済みで、条例による確認を依頼済み</t>
+          <t>No.12・No.15。いずれも確認事項として依頼済み</t>
         </is>
       </c>
       <c r="D29" s="7" t="n"/>
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="8" t="n"/>
     </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>未対応（資料待ち）</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>No.12・No.15。いずれも確認事項として依頼済み</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="n"/>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="8" t="n"/>
-    </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>注1）No.5は本レビューの指摘が的中し、評価の結論そのものを訂正した事例である。「3町の高齢者福祉計画に数値目標が1件も設定されていない」という所見は誤りであり、東川町は令和6〜8年度を対象とする事業の数値目標を6事業10項目以上設定していた。検索語に依存した判定の危うさが実証された。注2）この訂正は第10期にとって前向きな材料でもある。東川町には事業の数値目標を年度別に設定し実績と対比する仕組みが既にあるため、第10期の共通指標の掲載は同町では実現可能性が高く、美瑛町・東神楽町にはその様式を参考として示すことができる。注3）残る未対応2件（No.12・No.15）と一部対応1件（No.1）は、いずれも資料の受領を要する。確認事項No.7・No.11・No.37として依頼済みである。</t>
+    <row r="31" ht="84" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>注1）No.5は本レビューの指摘が的中し、評価の結論そのものを訂正した事例である。「3町の高齢者福祉計画に数値目標が1件も設定されていない」という所見は誤りであり、東川町は令和6〜8年度を対象とする事業の数値目標を6事業10項目以上設定していた。検索語に依存した判定の危うさが実証された。注2）この訂正は第10期にとって前向きな材料でもある。東川町には事業の数値目標を年度別に設定し実績と対比する仕組みが既にあるため、第10期の共通指標の掲載は同町では実現可能性が高く、美瑛町・東神楽町にはその様式を参考として示すことができる。注3）No.1も指摘が的中した。見える化B4・B5・B6系列の受領により5歳階級別の年齢調整を行った結果、所見7の結論（年齢構成を調整すると認定率は低下している）は裏付けられたが、65〜74歳は上昇しており「全年齢層で低下」は成り立たないこと、及び従来の説明「軽度は改善・中重度は悪化」が逆であることが判明した。後者は第10期の施策の重点を重度化防止から介護予防へ移す根拠となる。注4）残る未対応2件（No.12・No.15）は資料の受領を要する。確認事項No.7・No.11として依頼済みである。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C26:F26"/>
-    <mergeCell ref="A32:F32"/>
     <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="A31:F31"/>
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="C28:F28"/>
   </mergeCells>

--- a/output/第10期計画_第9期評価のレッドチームレビュー.xlsx
+++ b/output/第10期計画_第9期評価のレッドチームレビュー.xlsx
@@ -654,12 +654,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>18件の指摘を重大度・区分別に一覧化する。</t>
+          <t>26件の指摘を重大度・区分別に一覧化する。</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>重大7件・中9件・軽微2件</t>
+          <t>重大9件・中13件・軽微4件</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>6件（重大2・中3・軽微1）</t>
+          <t>8件（重大3・中3・軽微2）</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>6件（重大3・中3）</t>
+          <t>11件（重大4・中7）</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>6件（重大2・中3・軽微1）</t>
+          <t>7件（重大2・中3・軽微2）</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>18件</t>
+          <t>26件</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1066,7 +1066,7 @@
     <row r="32" ht="48" customHeight="1">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>注1）本レビューは受託者による自己点検である。外部の第三者によるレビューではないため、受託者が気づいていない前提の誤りは検出できない。注2）指摘のうち、受託者の判断で既に対応済みのものは含めていない。例えば健康とくらしの調査の対象者範囲の誤り（要支援者・要介護者を含まないこと）は、調査クロス集計・分析の妥当性レビュー（13・14シート）で自ら訂正済みである。注3）本レビューにより第9期の評価が全面的に誤っていると結論するものではない。18件のうち結論そのものが変わりうるのは7件であり、他は表現の限定又は根拠の追加で足りる。</t>
+          <t>注1）本レビューは受託者による自己点検である。外部の第三者によるレビューではないため、受託者が気づいていない前提の誤りは検出できない。注2）指摘のうち、受託者の判断で既に対応済みのものは含めていない。例えば健康とくらしの調査の対象者範囲の誤り（要支援者・要介護者を含まないこと）は、調査クロス集計・分析の妥当性レビュー（13・14シート）で自ら訂正済みである。注3）本レビューにより第9期の評価が全面的に誤っていると結論するものではない。26件のうち結論そのものが変わりうるのは9件であり、他は表現の限定又は根拠の追加で足りる。</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1115,7 +1115,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>指摘一覧（18件）</t>
+          <t>指摘一覧（26件）</t>
         </is>
       </c>
     </row>
@@ -1698,134 +1698,374 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="23" ht="48" customHeight="1">
+      <c r="A23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>推論</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>「受給率の低下分のほぼ全てが要介護5に由来する」（妥当性検証 13シート）</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>要介護度別の受給率の推移から低下分の帰属を述べているが、要介護5の受給者が減った理由を特定していない。</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>「低下分の大半は要介護5の受給率の低下による」に改める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="48" customHeight="1">
+      <c r="A24" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>「交付金の得点は第8期の取組を反映している」（複数の成果物）</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>No.2の指摘を受けて加えた限定であるが、その限定自体が調査の実施年度と交付年度の関係からの推論であり、調査要領で評価対象期間を直接確認していない。</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>「令和5年度に実施された調査であり、第9期（令和6年度〜）の取組は反映されていない」という確認できる範囲の限定に改める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>推論</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>「施設入所志向は心身の状態や経済状況ではなく支え手の有無で決まる」（調査クロス集計・分析 17シート）</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>施設志向群と在宅志向群で困りごと・移動制約・経済状況・フレイルに有意差がないことを根拠としているが、「有意差がない」ことは「関係がない」ことを意味しない。</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>「支え手の有無と強く結びついている」に改める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>推論</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>「朗根内地区は訪問・通所困難地域に該当する可能性が最も高い」（素案 第1章第7節）</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>人口233人、スクールバス依存、除雪率52.9％の組合せからの推論であり、判定基準として自ら定義した「事業所の通常の事業の実施地域」を確認していない。</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>推量の形は維持しつつ、「判定の根拠となる実施地域を確認していない」ことを明記する（不足資料No.2）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>推論</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>「第9期の人口推計は分母（総人口）の過大が原因で高齢化率が低い」（妥当性検証 03シート）</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>高齢化率の差を分母の過大で説明しているが、第9期計画と見える化の65歳以上人口はほぼ一致しており分母の差が主因であることは示せる一方、「原因」という語は要因の特定を意味する。</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>「高齢化率が低くなるのは、65歳以上人口がほぼ一致する一方で総人口が大きいためである」に改める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>推論</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>「訪問介護の高い利用強度は通所の供給が薄いことによる代替である」（素案 第2章第2節）</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>訪問介護1.87倍と通所0.74倍という2つの比率の対比からの推論であり、同一利用者における訪問と通所の組合せを確認していない。</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>「代替の可能性がある」の根拠が2つの比率の対比にとどまることを明記する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>枠組み</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>軽微</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>「本分析の値は調査報告書の公表値と完全に一致する」（調査クロス集計・分析 00・14シート）</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>一致を確認したのは広域連合全体及び町別の主要指標であり、全設問について確認したわけではない。</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>「広域連合全体及び町別の主要20指標について一致を確認した」に改め、確認した指標名を注記する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>軽微</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>国標準13段階の乗率を介護保険法施行令の内容として記述している（保険料の所得段階と低所得者軽減の検証 02シート）</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>施行令の条文を直接確認しておらず、複数の自治体公表資料により確認したものである。</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>出典を「介護保険法施行令第38条・第39条（複数の自治体公表資料により確認）」と明記する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>【集計】</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>重大</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>軽微</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>データ</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n">
+      <c r="B34" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C26" s="16" t="n">
+      <c r="E34" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="F34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>推論</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D35" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="F35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>枠組み</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="D26" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="F26" s="5" t="inlineStr"/>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>推論</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C27" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D27" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="F27" s="5" t="inlineStr"/>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>枠組み</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="n">
+      <c r="D36" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C28" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D28" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="F28" s="5" t="inlineStr"/>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="17" t="inlineStr">
+      <c r="E36" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="F36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B29" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="C29" s="18" t="n">
+      <c r="B37" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="D29" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E29" s="18" t="n">
-        <v>18</v>
-      </c>
-      <c r="F29" s="17" t="inlineStr"/>
-    </row>
-    <row r="31" ht="36" customHeight="1">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>注）重大と判定した7件は、指摘が正しければ所見の結論又は評価の範囲が変わるものである。No.1（年齢調整）・No.2（交付金の時点）・No.7（給付水準の要因）・No.8（利用率低下の要因）・No.9（成果指標の安定性）・No.13（評価範囲の誇張）・No.18（反証条件の欠如）。このうちNo.2とNo.13は、追加のデータがなくても記述の是正で対応できる。</t>
+      <c r="C37" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="D37" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E37" s="18" t="n">
+        <v>26</v>
+      </c>
+      <c r="F37" s="17" t="inlineStr"/>
+    </row>
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>注1）重大と判定した9件は、指摘が正しければ所見の結論又は評価の範囲が変わるものである。No.1（年齢調整）・No.2（交付金の時点）・No.7（給付水準の要因）・No.8（利用率低下の要因）・No.9（成果指標の安定性）・No.13（評価範囲の誇張）・No.18（反証条件の欠如）・No.19（要介護5への帰属）・No.20（交付金の評価対象期間）。このうちNo.2とNo.13は、追加のデータがなくても記述の是正で対応できる。注2）No.19〜No.26の8件は、令和8年7月29日に追加した再レビューの指摘である。検証結果が逆転した2件（No.5 3町の数値目標、No.1 年齢調整）の共通原因（①部分的な観測から全体を断定した、②不整合を説明する仮説を検証せずに事実として記述した）に照らして全成果物を再点検した結果である。詳細は「主張の根拠水準の棚卸しと再レビュー」04・05シートに示す。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A39:F39"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A32:F32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1837,7 +2077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2074,8 +2314,68 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+    <row r="11" ht="140" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>「交付金の得点は第8期の取組を反映している」（複数の成果物）</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>No.2の指摘を受けて加えた限定であるが、その限定自体が調査の実施年度と交付年度の関係からの推論であり、調査要領で評価対象期間を直接確認していない。評価項目により対象期間が異なる可能性がある（体制は調査時点、活動は前年度実績など）。</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>評価項目ごとに対象期間が異なる場合、「第8期の取組を反映している」という一律の説明は成り立たない。指摘への対応として加えた説明が、それ自体新たな未検証の断定になっている。</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>「令和5年度に実施された調査であり、第9期（令和6年度〜）の取組は反映されていない」という確認できる範囲の限定に改める。評価調書及び調査要領で確認する（不足資料No.5）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="140" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>軽微</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>国標準13段階の乗率を介護保険法施行令の内容として記述している（保険料の所得段階と低所得者軽減の検証 02シート）</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>施行令の条文を直接確認しておらず、複数の自治体公表資料により確認したものである。出典の水準が原典ではない。</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>自治体の資料に誤りがある可能性は低いが、出典として施行令を示すのであれば条文の確認を要する。</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>出典を「介護保険法施行令第38条・第39条（複数の自治体公表資料により確認）」と明記する。第10期の標準乗率は政令改正により定まる（不足資料No.11）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>注1）No.1（年齢調整）とNo.2（交付金の時点）は、いずれも「評価の結論が逆になりうる」性質の指摘である。No.1は調整済み指標（W144）が悪化していることと矛盾し、No.2は評価対象期間そのものがずれている。注2）No.3・No.4は金額・水準の確定性に関する指摘である。概算値であることを明記すれば足りるが、具体的な金額を示している以上、確定値による置換えが望ましい。</t>
         </is>
@@ -2084,8 +2384,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2097,7 +2397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2334,8 +2634,158 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+    <row r="11" ht="140" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>「受給率の低下分のほぼ全てが要介護5に由来する」（妥当性検証 13シート）</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>要介護度別の受給率の推移から低下分の帰属を述べているが、要介護5の受給者が減った理由を特定していない。死亡、施設入所、認定の変化、区域外への転出が並立する。「由来する」は要因の特定を意味する語であり、差の帰属の計算とは別のものである。</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>要介護5の受給者の減少が死亡によるものであれば、サービス供給の問題ではなく人口動態の問題である。この場合、第10期の整備方針の根拠にはならない。</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>「低下分の大半は要介護5の受給率の低下による」に改める。要因の特定には認定・給付データを要する（不足資料No.8）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="140" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>「施設入所志向は心身の状態や経済状況ではなく支え手の有無で決まる」（調査クロス集計・分析 17シート）</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>施設志向群と在宅志向群で困りごと・移動制約・経済状況・フレイルに有意差がないことを根拠としているが、「有意差がない」ことは「関係がない」ことを意味しない。標本規模による検出力を検討していない。</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>検出力が不足している場合、実際には差があっても有意にならない。分母は施設志向1,418人・在宅志向2,251人であり検出力は高いが、示すべきは検出力ではなく効果量の小ささである。</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>「支え手の有無と強く結びついている」に改める。有意差がない項目については差の大きさと信頼区間を併記する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="140" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>「朗根内地区は訪問・通所困難地域に該当する可能性が最も高い」（素案 第1章第7節）</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>人口233人、スクールバス依存、除雪率52.9％の組合せからの推論であり、判定基準として自ら定義した「事業所の通常の事業の実施地域」を確認していない。判定の根拠そのものが未取得である。</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>朗根内地区が複数の事業所の実施地域に含まれていれば、困難地域には該当しない。逆に、より人口の多い地区が実施地域から外れている可能性もある。</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>推量の形は維持しつつ、「判定の根拠となる実施地域を確認していない」ことを明記する（不足資料No.2）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="140" customHeight="1">
+      <c r="A14" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>「第9期の人口推計は分母（総人口）の過大が原因で高齢化率が低い」（妥当性検証 03シート）</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>高齢化率の差を分母の過大で説明しているが、第9期計画と見える化の65歳以上人口はほぼ一致しており分母の差が主因であることは示せる一方、「原因」という語は要因の特定を意味する。分母の差が生じた理由（住基と国勢調査の基準差、社会増の見込み）は特定していない。</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>分母の差が住基と国勢調査の基準差によるものであれば、推計の誤りではなく基準の違いである。社会増の見込みの過大であれば推計の見直しを要する。対応が正反対になる。</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>「高齢化率が低くなるのは、65歳以上人口がほぼ一致する一方で総人口が大きいためである」に改める。町別人口の実績により検証する（不足資料No.3）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="140" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>「訪問介護の高い利用強度は通所の供給が薄いことによる代替である」（素案 第2章第2節）</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>訪問介護1.87倍と通所0.74倍という2つの比率の対比からの推論であり、同一利用者における訪問と通所の組合せを確認していない。現在も推量の形で記述しているが、推量の根拠が2つの比率の対比のみであることを示していない。</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>訪問介護の利用者と通所介護の利用者が別の層であれば、代替関係は成り立たない。世帯構成や移動制約により訪問を選択している可能性もある。</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>「代替の可能性がある」の根拠が2つの比率の対比にとどまることを明記する。ケアプランのサービス構成により検証する（不足資料No.8）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>注1）No.7・No.8・No.10は、いずれも「同じ事実から逆の政策的含意が導かれうる」性質の指摘である。供給が足りないのか需要が少ないのか、施設に入れないのか在宅を選んでいるのかで、第10期の整備方針が変わる。注2）これらの区別には、区域内外の利用の別、未利用認定者の要因別内訳、本人・家族の意向が必要である。調査クロス集計・分析15シートで意向の一部は把握したが、給付側の情報（確認No.23・30）が不足している。</t>
         </is>
@@ -2345,7 +2795,7 @@
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A17:F17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2357,7 +2807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2594,8 +3044,38 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+    <row r="11" ht="140" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>軽微</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>「本分析の値は調査報告書の公表値と完全に一致する」（調査クロス集計・分析 00・14シート）</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>一致を確認したのは広域連合全体及び町別の主要指標であり、全設問について確認したわけではない。確認の範囲を示さずに「完全に一致」と記述している。</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>確認していない設問で不一致がある可能性を排除できない。個票データの再現性の主張が過大になる。</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>「広域連合全体及び町別の主要20指標について一致を確認した」に改め、確認した指標名を注記する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>注1）No.13は本レビューで最も重い指摘である。第9期の評価のうち、事業が計画どおり実施されたかというプロセス評価が実績未受領のため空白であり、現状は「計画の記載事項の検証」と「外部評価の分析」にとどまる。成果物の表題と業務工程管理表の進捗の表現を改める必要がある。注2）No.16は、指摘が正しくても評価そのものは変わらないが、3町・広域連合の実務者の納得を得るために不可欠な視点である。</t>
         </is>
@@ -2603,9 +3083,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A13:F13"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3382,7 +3862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3404,7 +3884,7 @@
     <row r="2" ht="56" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>18件の指摘について、記述の修正・追加分析・確認事項のいずれで対応するかを整理する。追加のデータがなくても対応できるものと、資料の受領を要するものを区別する。</t>
+          <t>26件の指摘について、記述の修正・追加分析・確認事項のいずれで対応するかを整理する。追加のデータがなくても対応できるものと、資料の受領を要するものを区別する。</t>
         </is>
       </c>
     </row>
@@ -4075,107 +4555,387 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="23" ht="64" customHeight="1">
+      <c r="A23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>「受給率の低下分のほぼ全てが要介護5に由来する」</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>記述の修正</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>「由来する」を「低下分の大半は要介護5の受給率の低下による」に改める。要因の特定を第10期の課題として位置づける</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>認定・給付データ（不足資料No.8）</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="64" customHeight="1">
+      <c r="A24" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>「交付金の得点は第8期の取組を反映している」</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>記述の修正</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>「第8期の取組を反映している」を「令和5年度に実施された調査であり第9期の取組は反映されていない」に改める</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>評価調書・調査要領（不足資料No.5）</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="64" customHeight="1">
+      <c r="A25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>「施設入所志向は心身の状態や経済状況ではなく支え手の有無で決まる」</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>記述の修正</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>「支え手の有無で決まる」を「支え手の有無と強く結びついている」に改め、差の大きさと信頼区間を併記する</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="64" customHeight="1">
+      <c r="A26" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>「朗根内地区は訪問・通所困難地域に該当する可能性が最も高い」</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>記述の修正</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>推量の形は維持し、判定の根拠となる実施地域を確認していないことを明記する</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>事業所の実施地域（不足資料No.2）</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="64" customHeight="1">
+      <c r="A27" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>「第9期の人口推計は分母</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>記述の修正</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>「分母の過大が原因」を「65歳以上人口がほぼ一致する一方で総人口が大きいため」に改める</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>町別人口の実績（不足資料No.3）</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="64" customHeight="1">
+      <c r="A28" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>「訪問介護の高い利用強度は通所の供給が薄いことによる代替である」</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>記述の修正</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>「代替の可能性がある」の根拠が2つの比率の対比にとどまることを明記する</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>ケアプランのサービス構成（不足資料No.8）</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="64" customHeight="1">
+      <c r="A29" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>軽微</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>「本分析の値は調査報告書の公表値と完全に一致する」</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>記述の修正</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>「完全に一致」を「主要20指標について一致を確認した」に改め、確認した指標名を注記する</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="64" customHeight="1">
+      <c r="A30" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>軽微</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>国標準13段階の乗率を介護保険法施行令の内容として記述している</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>記述の修正</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>出典を「施行令第38条・第39条（複数の自治体公表資料により確認）」と明記する</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>介護保険法施行令（不足資料No.11）</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>【対応の集計】</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26" ht="44" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>追加のデータなしで対応できる</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>記述の修正・表現の限定・注記の追加により対応する。計画素案の次稿で反映する</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
-      <c r="G26" s="8" t="n"/>
-    </row>
-    <row r="27" ht="44" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34" ht="44" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>記述の修正により対応できる</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>記述の修正・表現の限定・注記の追加により対応する。計画素案の次稿で反映する。再レビューの8件（No.19〜26）を含む</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="7" t="n"/>
+      <c r="F34" s="7" t="n"/>
+      <c r="G34" s="8" t="n"/>
+    </row>
+    <row r="35" ht="44" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>受領済の資料で対応できる</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n">
+      <c r="B35" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>3町の計画の再点検（No.5）、反証条件の明示（No.18・実施済）</t>
         </is>
       </c>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="8" t="n"/>
-    </row>
-    <row r="28" ht="44" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="7" t="n"/>
+      <c r="G35" s="8" t="n"/>
+    </row>
+    <row r="36" ht="44" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>資料の受領を要する</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n">
+      <c r="B36" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>No.1（見える化B4系列）・No.3（決算・基金）・No.4（条例）・No.12（町別人口実績）・No.15（自己評価）</t>
         </is>
       </c>
-      <c r="D28" s="7" t="n"/>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
-      <c r="G28" s="8" t="n"/>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>注1）18件のうち11件は追加のデータなしで対応できる。記述の限定と注記の追加により、評価の結論を変えずに信頼性を高めることができる。注2）最も優先すべきはNo.1（年齢調整）とNo.13（評価範囲）である。No.1は見える化B4系列の取得により検証でき、No.13は表題と進捗の表現の見直しで足りる。注3）本レビューの指摘は、業務工程管理表の確認事項一覧に反映する。</t>
+      <c r="D36" s="7" t="n"/>
+      <c r="E36" s="7" t="n"/>
+      <c r="F36" s="7" t="n"/>
+      <c r="G36" s="8" t="n"/>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>注1）26件のうち19件は記述の修正により対応できる。記述の限定と注記の追加により、評価の結論を変えずに信頼性を高めることができる。注2）最も優先すべきはNo.1（年齢調整）とNo.13（評価範囲）である。No.1は見える化B4系列の取得により検証でき、No.13は表題と進捗の表現の見直しで足りる。注3）本レビューの指摘は、業務工程管理表の確認事項一覧に反映する。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="C35:G35"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="A38:G38"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C36:G36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4187,7 +4947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4798,122 +5558,383 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="23" ht="76" customHeight="1">
+      <c r="A23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>要介護5への帰属を「由来する」と断定</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>対応中</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>主張の根拠水準の棚卸し03シートで断定箇所として特定した。妥当性検証13シート及び素案の該当箇所を「低下分の大半は要介護5の受給率の低下による」に改める。要因の特定には認定・給付データを要するため、第10期の検討課題として位置づける。</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>主張の根拠水準の棚卸し 03シート
+妥当性検証 13シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="76" customHeight="1">
+      <c r="A24" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>交付金の評価対象期間を未確認のまま断定</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>対応中</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>No.2への対応として加えた「第8期の取組を反映」という説明が、それ自体未検証の推論であることを特定した。確認できる範囲の限定（令和5年度実施の調査であり第9期の取組は反映されていない）に改める。評価調書及び調査要領で確認する。</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>主張の根拠水準の棚卸し 03シート
+保険料と施策評価の他団体比較 04シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="76" customHeight="1">
+      <c r="A25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>有意差がないことを「関係がない」と解釈</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>対応中</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>「支え手の有無で決まる」を「支え手の有無と強く結びついている」に改める。有意差がない項目については差の大きさと信頼区間を併記する。</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>調査クロス集計・分析 17シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="76" customHeight="1">
+      <c r="A26" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>困難地域の判定基準そのものが未取得</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>対応中</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>推量の形は維持し、判定の根拠となる事業所の実施地域を確認していないことを明記する。</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>素案 第1章第7節</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="76" customHeight="1">
+      <c r="A27" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>高齢化率の差を「分母の過大が原因」と断定</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>対応中</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>「65歳以上人口がほぼ一致する一方で総人口が大きいため」に改める。分母の差が生じた理由（基準差か社会増の見込みか）は町別人口の実績により検証する。</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>妥当性検証 03シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="76" customHeight="1">
+      <c r="A28" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>訪問と通所の代替関係の根拠を明示していない</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>対応中</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>推量の形は維持し、根拠が訪問1.87倍・通所0.74倍という2つの比率の対比にとどまることを明記する。</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>素案 第2章第2節</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="76" customHeight="1">
+      <c r="A29" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>軽微</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>公表値との一致の確認範囲を示していない</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>対応中</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>「完全に一致」を「広域連合全体及び町別の主要20指標について一致を確認した」に改め、確認した指標名を注記する。</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>調査クロス集計・分析 00・14シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="76" customHeight="1">
+      <c r="A30" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>軽微</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>施行令の条文を直接確認していない</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>対応中</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>出典を「介護保険法施行令第38条・第39条（複数の自治体公表資料により確認）」と明記する。</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>保険料の所得段階と低所得者軽減の検証 02シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>【対応状況の集計】</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>対応済</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n">
+      <c r="B34" s="16" t="n">
         <v>13</v>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>記述の修正・表現の限定・注記の追加を実施した</t>
         </is>
       </c>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="8" t="n"/>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="7" t="n"/>
+      <c r="F34" s="8" t="n"/>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>対応中</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>No.19〜No.26。令和8年7月29日の再レビューで新たに特定した指摘であり、改める記述を確定したうえで各成果物に反映する</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="8" t="n"/>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>訂正（指摘的中）</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n">
+      <c r="B36" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>No.5（3町の数値目標）とNo.1（年齢調整）。いずれも指摘が的中し、評価の記述を訂正した。特にNo.1では「軽度は改善・中重度は悪化」という従来の説明が逆であることが判明し、施策の重点に影響する</t>
         </is>
       </c>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="8" t="n"/>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="D36" s="7" t="n"/>
+      <c r="E36" s="7" t="n"/>
+      <c r="F36" s="8" t="n"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>対応済（確認待ち）</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n">
+      <c r="B37" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>No.4。注記済みで、条例による確認を依頼済み</t>
         </is>
       </c>
-      <c r="D28" s="7" t="n"/>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="8" t="n"/>
-    </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="8" t="n"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>未対応（資料待ち）</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n">
+      <c r="B38" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>No.12・No.15。いずれも確認事項として依頼済み</t>
         </is>
       </c>
-      <c r="D29" s="7" t="n"/>
-      <c r="E29" s="7" t="n"/>
-      <c r="F29" s="8" t="n"/>
-    </row>
-    <row r="31" ht="84" customHeight="1">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="D38" s="7" t="n"/>
+      <c r="E38" s="7" t="n"/>
+      <c r="F38" s="8" t="n"/>
+    </row>
+    <row r="40" ht="84" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
         <is>
           <t>注1）No.5は本レビューの指摘が的中し、評価の結論そのものを訂正した事例である。「3町の高齢者福祉計画に数値目標が1件も設定されていない」という所見は誤りであり、東川町は令和6〜8年度を対象とする事業の数値目標を6事業10項目以上設定していた。検索語に依存した判定の危うさが実証された。注2）この訂正は第10期にとって前向きな材料でもある。東川町には事業の数値目標を年度別に設定し実績と対比する仕組みが既にあるため、第10期の共通指標の掲載は同町では実現可能性が高く、美瑛町・東神楽町にはその様式を参考として示すことができる。注3）No.1も指摘が的中した。見える化B4・B5・B6系列の受領により5歳階級別の年齢調整を行った結果、所見7の結論（年齢構成を調整すると認定率は低下している）は裏付けられたが、65〜74歳は上昇しており「全年齢層で低下」は成り立たないこと、及び従来の説明「軽度は改善・中重度は悪化」が逆であることが判明した。後者は第10期の施策の重点を重度化防止から介護予防へ移す根拠となる。注4）残る未対応2件（No.12・No.15）は資料の受領を要する。確認事項No.7・No.11として依頼済みである。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A24:F24"/>
+  <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C34:F34"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C36:F36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_第9期評価のレッドチームレビュー.xlsx
+++ b/output/第10期計画_第9期評価のレッドチームレビュー.xlsx
@@ -654,12 +654,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>26件の指摘を重大度・区分別に一覧化する。</t>
+          <t>29件の指摘を重大度・区分別に一覧化する。</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>重大9件・中13件・軽微4件</t>
+          <t>重大11件・中14件・軽微4件</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>8件（重大3・中3・軽微2）</t>
+          <t>9件（重大4・中3・軽微2）</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>11件（重大4・中7）</t>
+          <t>12件（重大4・中8・軽微0）</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>7件（重大2・中3・軽微2）</t>
+          <t>8件（重大3・中3・軽微2）</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>26件</t>
+          <t>29件</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1066,7 +1066,7 @@
     <row r="32" ht="48" customHeight="1">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>注1）本レビューは受託者による自己点検である。外部の第三者によるレビューではないため、受託者が気づいていない前提の誤りは検出できない。注2）指摘のうち、受託者の判断で既に対応済みのものは含めていない。例えば健康とくらしの調査の対象者範囲の誤り（要支援者・要介護者を含まないこと）は、調査クロス集計・分析の妥当性レビュー（13・14シート）で自ら訂正済みである。注3）本レビューにより第9期の評価が全面的に誤っていると結論するものではない。26件のうち結論そのものが変わりうるのは9件であり、他は表現の限定又は根拠の追加で足りる。</t>
+          <t>注1）本レビューは受託者による自己点検である。外部の第三者によるレビューではないため、受託者が気づいていない前提の誤りは検出できない。注2）指摘のうち、受託者の判断で既に対応済みのものは含めていない。例えば健康とくらしの調査の対象者範囲の誤り（要支援者・要介護者を含まないこと）は、調査クロス集計・分析の妥当性レビュー（13・14シート）で自ら訂正済みである。注3）本レビューにより第9期の評価が全面的に誤っていると結論するものではない。29件のうち結論そのものが変わりうるのは11件であり、他は表現の限定又は根拠の追加で足りる。</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1115,7 +1115,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>指摘一覧（26件）</t>
+          <t>指摘一覧（29件）</t>
         </is>
       </c>
     </row>
@@ -1910,168 +1910,1048 @@
     </row>
     <row r="30" ht="48" customHeight="1">
       <c r="A30" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>地域差指数の3要素の分解を要因の按分に用いていた（妥当性検証 所見1、素案 第2章第2節、保険料と施策評価の他団体比較 03シート）</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>受給率×受給者単価が給付月額指数に一致することを前提に按分していたが、上川管内21保険者のうち16保険者で0.03を超えてずれる。</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>分解による按分の記述を撤回し、4要素を並列の指標として示す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>枠組み</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>給付水準を全国比のみで評価し、管内の位置を確認していなかった（妥当性検証 所見1・2、素案 第2章第2節・第3章）</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>給付月額指数1.08を「全国を8％上回る」として第9期の課題としてきたが、上川管内21保険者のなかでは8〜10位（比布町・剣淵町と同値）であり、管内中位値1.05に近い。</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>第9期の評価に管内の位置と長期の推移を加える。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>推論</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>自給率と給付水準の関係について、外れ値に駆動された相関を示しかけた（地域差の分析06シートの検討過程）</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>単一市町村保険者19件で相関を計算するとr＝0.53となり「自給率が低いほど給付水準が高い」という関係が見えるが、これは自給率0.0％の2村（占冠村0.82・音威子府村0.73）による。</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>本表では両方の値を示し、除外の理由を明記した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>データ</t>
         </is>
       </c>
-      <c r="C30" s="15" t="inlineStr">
+      <c r="C33" s="15" t="inlineStr">
         <is>
           <t>軽微</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>国標準13段階の乗率を介護保険法施行令の内容として記述している（保険料の所得段階と低所得者軽減の検証 02シート）</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>施行令の条文を直接確認しておらず、複数の自治体公表資料により確認したものである。</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>出典を「介護保険法施行令第38条・第39条（複数の自治体公表資料により確認）」と明記する。</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>【集計】</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="32" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>重大</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>軽微</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>データ</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n">
+      <c r="B37" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="C34" s="16" t="n">
+      <c r="D37" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="F37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>推論</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C38" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="D38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="F38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>枠組み</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="D34" s="16" t="n">
+      <c r="C39" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E34" s="16" t="n">
+      <c r="E39" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="F34" s="5" t="inlineStr"/>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>推論</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="n">
+      <c r="F39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="C40" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="D40" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="C35" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="D35" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="F35" s="5" t="inlineStr"/>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>枠組み</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="C36" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D36" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E36" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="F36" s="5" t="inlineStr"/>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="17" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="B37" s="18" t="n">
-        <v>9</v>
-      </c>
-      <c r="C37" s="18" t="n">
-        <v>13</v>
-      </c>
-      <c r="D37" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="E37" s="18" t="n">
-        <v>26</v>
-      </c>
-      <c r="F37" s="17" t="inlineStr"/>
-    </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" s="12" t="inlineStr">
-        <is>
-          <t>注1）重大と判定した9件は、指摘が正しければ所見の結論又は評価の範囲が変わるものである。No.1（年齢調整）・No.2（交付金の時点）・No.7（給付水準の要因）・No.8（利用率低下の要因）・No.9（成果指標の安定性）・No.13（評価範囲の誇張）・No.18（反証条件の欠如）・No.19（要介護5への帰属）・No.20（交付金の評価対象期間）。このうちNo.2とNo.13は、追加のデータがなくても記述の是正で対応できる。注2）No.19〜No.26の8件は、令和8年7月29日に追加した再レビューの指摘である。検証結果が逆転した2件（No.5 3町の数値目標、No.1 年齢調整）の共通原因（①部分的な観測から全体を断定した、②不整合を説明する仮説を検証せずに事実として記述した）に照らして全成果物を再点検した結果である。詳細は「主張の根拠水準の棚卸しと再レビュー」04・05シートに示す。</t>
+      <c r="E40" s="18" t="n">
+        <v>29</v>
+      </c>
+      <c r="F40" s="17" t="inlineStr"/>
+    </row>
+    <row r="42" ht="72" customHeight="1">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>注1）重大と判定した11件は、指摘が正しければ所見の結論又は評価の範囲が変わるものである。No.1（年齢調整）・No.2（交付金の時点）・No.7（給付水準の要因）・No.8（利用率低下の要因）・No.9（成果指標の安定性）・No.13（評価範囲の誇張）・No.18（反証条件の欠如）・No.19（要介護5への帰属）・No.20（交付金の評価対象期間）・No.27（地域差指数の分解）・No.28（管内の位置の未確認）。このうちNo.2とNo.13は、追加のデータがなくても記述の是正で対応できる。注2）No.19〜No.26の8件は令和8年7月29日、No.27〜No.29の3件は令和8年7月30日に追加した再レビューの指摘である。検証結果が逆転した2件（No.5 3町の数値目標、No.1 年齢調整）の共通原因（①部分的な観測から全体を断定した、②不整合を説明する仮説を検証せずに事実として記述した）に照らして全成果物を再点検した結果である。詳細は「主張の根拠水準の棚卸しと再レビュー」04・05シートに示す。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A39:F39"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A42:F42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>データと出典への指摘</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="56" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>用いたデータの時点、範囲、確定性に関する指摘。評価しようとしている期間のデータを使っているか、結論を支えるために必要な系列が揃っているか、概算値を確定値のように扱っていないかを点検した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>重大度</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>対象となる主張</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>指摘（成り立たない可能性）</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>別の説明・想定される反論</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="140" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>「年齢層をそろえると認定率は低下している」（妥当性検証 所見7、素案 第3章第4節）</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>根拠としているのは合計認定率・75歳以上・85歳以上の3系列のみで、65〜74歳の認定率を確認していない。75歳以上という括りの内部でも75〜84歳と85歳以上の構成比が変化しているため、75歳以上の粗率は依然として年齢構成の影響を受ける。真の年齢調整（5歳階級別の直接法）は行っていない。</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>65〜74歳の認定率が上昇していれば、「全年齢層で低下」という主張は崩れる。また、性・年齢調整済み要介護2以上認定率（W144）は9.25％で全国を上回り、変化率も＋1.76と悪化している。調整済みの指標が悪化しているのに「調整すると低下」と述べるのは、少なくとも説明が不足している。</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>見える化B4系列の年齢階級別認定率（65〜74歳を含む）を取得し、5歳階級別の直接法により再計算する。W144との整合を「軽度は改善・中重度は悪化」で説明するのであれば、要介護度別の認定率の推移でそれを実証する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="140" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>交付金の評価得点を「第9期の評価」として用いている（妥当性検証 所見18・19、保険料と施策評価の他団体比較 04シート）</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>用いたのは令和5年調査（令和6年度分指標）である。調査は令和5年度に実施され、評価対象は主に令和4年度の実施状況である。第9期は令和6年度からであるから、この得点は第9期の取組をほとんど反映していない。実質的には第8期の評価である。</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>「活動指標群が全国の23.2％」は第8期末の記録・報告体制を示すものであり、第9期に改善している可能性を排除できない。第9期の評価としてこれを用いると、保険者の第9期の努力を不当に低く評価することになる。</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>令和6年調査・令和7年調査（令和7年度分・令和8年度分指標）の得点を取得し、経年で比較する。取得できない場合は、「第8期の取組を反映した評価である」と明記して用いる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="140" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>「第9期は2年で約42百万円の剰余が生じている」（妥当性検証 所見9、素案 第6章第6節）</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>必要保険料月額（見える化P4）と条例基準額の差に被保険者数と12月を乗じた概算である。令和6年度の値は令和8年1月時点の実績を年度換算したものであり、確定値ではない。決算及び基金の積立実績で確認していない。</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>年度末までの給付費の変動、地域支援事業費の執行残、国庫負担金の精算等により、決算ベースの剰余は概算と大きく異なりうる。42百万円という具体的な金額を示すと、決算と食い違ったときに評価全体の信頼を損なう。</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>「概算」であることを金額の直後に明記する。決算書及び基金の積立・取崩実績を受領し、確定値に置き換える（確認No.16）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="140" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>第7期の保険料基準額を6,077円に訂正した（保険料と施策評価の他団体比較 02シート、素案 第6章第6節）</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>訂正の根拠は「剰余の累計＋159円／月と整合するのは6,077円だけである」という内部整合性のみで、条例で確認していない。＋159円という数字自体が誤っていれば、訂正が誤りとなる。</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>＋159円の出所は第9稿の記載であり、その根拠も未確認である。6,077円と5,900円のいずれかが正しいのではなく、両方が誤っている可能性もある。</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>第7期（平成30〜令和2年度）の保険料条例により確認する（確認No.32）。確認できるまで、素案には両論を併記するか、記載を保留する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="140" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>「3町の高齢者福祉計画に数値目標が1件も設定されていない」（妥当性検証 所見5）</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>判定の根拠は「数値目標」「目標値」という語の全文検索による出現回数である。語が使われていなくても、表や本文に実質的な目標値が示されている可能性を排除していない。</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>3町の計画に「○年度までに△件」のような記述が、「数値目標」という語を使わずに含まれている場合、判定は誤りとなる。3町に対して「目標が1件もない」と断じることは関係上の影響も大きい。</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>3町の計画の各章を目視で確認し、数値を伴う記述の有無を再点検する。そのうえで「進行管理の対象として明示された数値目標がない」等、判定の範囲を限定した表現に改める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="140" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>軽微</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>認定率の実績を「令和8年3月末21.8％」と表記している（妥当性検証 02シート）</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>令和8年3月末は令和7年度末である。第9期は令和6〜8年度であるから、最終年度（令和8年度）の実績はまだ出ていない。現時点の評価は中間評価であって、期の評価ではない。</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>「令和8年3月末」という表記は、令和8年度末と読まれるおそれがある。</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>「令和7年度末（令和8年3月末）」と年度を明記する。第9期の最終評価は令和9年3月末の実績によることを明示する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="140" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>「交付金の得点は第8期の取組を反映している」（複数の成果物）</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>No.2の指摘を受けて加えた限定であるが、その限定自体が調査の実施年度と交付年度の関係からの推論であり、調査要領で評価対象期間を直接確認していない。評価項目により対象期間が異なる可能性がある（体制は調査時点、活動は前年度実績など）。</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>評価項目ごとに対象期間が異なる場合、「第8期の取組を反映している」という一律の説明は成り立たない。指摘への対応として加えた説明が、それ自体新たな未検証の断定になっている。</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>「令和5年度に実施された調査であり、第9期（令和6年度〜）の取組は反映されていない」という確認できる範囲の限定に改める。評価調書及び調査要領で確認する（不足資料No.5）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="140" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>地域差指数の3要素の分解を要因の按分に用いていた（妥当性検証 所見1、素案 第2章第2節、保険料と施策評価の他団体比較 03シート）</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>受給率×受給者単価が給付月額指数に一致することを前提に按分していたが、上川管内21保険者のうち16保険者で0.03を超えてずれる。当広域連合では受給率1.08×受給者単価1.06＝1.145に対し給付月額指数は1.08であり、＋0.065のずれがある。しかもずれは全保険者で正の方向に偏っており（平均＋0.063）、偶然の誤差ではない。</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>恒等式として用いれば給付水準を6％過大に評価する。給付月額指数と認定率指数は性・年齢調整後であるが、受給率指数と受給者単価指数には調整の表示がなく、調整の有無が異なる指数を掛け合わせている可能性がある。</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>分解による按分の記述を撤回し、4要素を並列の指標として示す。要因の特定は保険者間の分散の説明（管内21保険者の回帰）による。D49の指標定義を確認する（不足資料No.16）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="140" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>軽微</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>国標準13段階の乗率を介護保険法施行令の内容として記述している（保険料の所得段階と低所得者軽減の検証 02シート）</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>施行令の条文を直接確認しておらず、複数の自治体公表資料により確認したものである。出典の水準が原典ではない。</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>自治体の資料に誤りがある可能性は低いが、出典として施行令を示すのであれば条文の確認を要する。</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>出典を「介護保険法施行令第38条・第39条（複数の自治体公表資料により確認）」と明記する。第10期の標準乗率は政令改正により定まる（不足資料No.11）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>注1）No.1（年齢調整）とNo.2（交付金の時点）は、いずれも「評価の結論が逆になりうる」性質の指摘である。No.1は調整済み指標（W144）が悪化していることと矛盾し、No.2は評価対象期間そのものがずれている。注2）No.3・No.4は金額・水準の確定性に関する指摘である。概算値であることを明記すれば足りるが、具体的な金額を示している以上、確定値による置換えが望ましい。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A15:F15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>推論への指摘</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="56" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>データから結論を導く過程に関する指摘。同じ事実を説明できる別の仮説、特に逆の政策的含意をもつ仮説を併記した。因果の方向を特定できているかも点検した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>重大度</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>対象となる主張</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>指摘（成り立たない可能性）</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>別の説明・想定される反論</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="140" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>「給付水準の高さは施設・居住系サービスの受給率に集約される」（妥当性検証 所見1）</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>地域差指数を認定率・受給率・単価に分解しているが、これらは独立ではない。施設が多ければ受給率も単価も同時に上がるため、「受給率に集約される」という表現は要因の特定になっていない。また、因果の方向（施設があるから給付が高い／需要があるから施設がある）を特定していない。</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>介護老人福祉施設の定員が234人から160人へ減少しているにもかかわらず施設・居住系の受給率が高いという事実は、この説明と緊張関係にある。区域外施設の利用（住所地特例を含む）が多いことによる可能性があり、その場合、区域内の整備方針を論じる根拠にはならない。</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>区域内施設の利用者数と区域外施設の利用者数を分けて把握する。自給率（δ2・δ3）の算定（国保連の給付実績情報と指定事業所台帳の突合）により検証する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="140" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>「介護サービス利用率の低下は供給制約による」という含意（妥当性検証 所見2、素案 第2章第2節3）</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>認定者が増え受給者が減ったという事実だけでは、供給制約は導けない。未利用の理由には、軽度で自立している、申請だけ先行した、家族介護で足りている、経済的理由、供給がない、が並立する。素案では要因分解の必要性を書いているが、他の資料では「課題」として断定的に扱っている箇所がある。</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>第9期に認定を受けやすくする働きかけ（申請勧奨）を行った結果として認定者が増え、そのうち軽度者が利用に至っていないだけであれば、供給制約ではなく認定行政の変化である。この場合、施策の方向は逆になる。</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>居宅サービス計画未作成者の要介護度別内訳を把握する。新規認定者数と認定申請件数の推移を確認する。断定的な表現を「要因の分解を要する」に統一する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="140" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>「成果は全国トップ級」（妥当性検証 所見19、保険料と施策評価の他団体比較 04・05シート）</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>成果指標（目標Ⅳ）は要介護度の変化率であり、認定者約1,960人という母集団では単年度の変動が大きい。統計的な安定性を検証していない。また、長期指標が良好である一方、直近の変化率は全国と逆方向に悪化している。</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>少数の重度化事例の増減で指標が大きく振れる。「全国の0.51倍」という値は、実数でみれば数十人規模の差にすぎない可能性がある。「トップ級」という表現は一時点の結果を過大に評価している。</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>目標Ⅳの各指標の分子・分母の実数を確認する。複数年の推移でみたうえで、「全国トップ級」という表現を「令和6年度分指標では全国を上回る」に改める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="140" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>「重度者の在宅化が進む」（妥当性検証 所見3）</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>要介護5の在宅・居住系割合が31.3％から54.6％へ上昇したことを「在宅化」と表現しているが、施設に入れないから在宅にいるのか、在宅を支える体制ができたから在宅にいるのかで意味が正反対になる。この区別を論証していない。</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>24時間対応の3サービスが区域内に存在しないことを考えると、在宅を支える体制がない中で在宅にとどまっている、すなわち家族介護への転嫁である可能性が高い。「在宅化が進む」という表現は、政策の成果と誤読されうる。</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>「施設定員の縮小と同時に進んでおり、在宅の支援体制が整った結果ではない」と明記する。本人・家族の状況（調査クロス集計・分析 15シート）と併せて記述する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="140" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>施策の「評価可能性」判定（部分評価6施策・指標不足13施策）（施策体系新旧対照表 施策の新旧対照）</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>計画文書の記載のみによる机上評価であり、事業が実際に行われたか、効果があったかは一切見ていない。「指標不足」は計画の記載の問題であって、施策の良否ではない。</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>指標が計画に書かれていなくても、事業として実施され成果を上げている可能性がある。19施策のうち13を「指標不足」と示すと、施策そのものが不十分であったと受け取られるおそれがある。</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>「計画記載上の評価可能性」であることを表題と注に明記する。令和6〜8年度の事業実績（確認No.5）を受領後、実施状況の評価を別に行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="140" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>東川町の人口推計が「社人研から大きく上振れしている」（妥当性検証 所見4）</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>第9期計画は住民基本台帳ベース、社人研は国勢調査ベースであり、基準そのものが異なる。美瑛町の乖離（＋2.2〜3.2％）は「住基と国勢調査の基準差」と説明しているのに、東川町の＋18.5％だけを「上振れ」と断じており、基準差と社会増の分離ができていない。</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>東川町は移住施策により実際に社会増が続いている可能性があり、その場合は社人研推計が過小である。どちらが正しいかを検証せずに「上振れ」と評価するのは片側に寄っている。</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>令和6年・令和7年の住民基本台帳実績を両推計に当てはめ、どちらが実績に近いかを検証する。そのうえで第10期の人口推計の基礎とする系列を決定する（確認No.14）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="140" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>「受給率の低下分のほぼ全てが要介護5に由来する」（妥当性検証 13シート）</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>要介護度別の受給率の推移から低下分の帰属を述べているが、要介護5の受給者が減った理由を特定していない。死亡、施設入所、認定の変化、区域外への転出が並立する。「由来する」は要因の特定を意味する語であり、差の帰属の計算とは別のものである。</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>要介護5の受給者の減少が死亡によるものであれば、サービス供給の問題ではなく人口動態の問題である。この場合、第10期の整備方針の根拠にはならない。</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>「低下分の大半は要介護5の受給率の低下による」に改める。要因の特定には認定・給付データを要する（不足資料No.8）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="140" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>「施設入所志向は心身の状態や経済状況ではなく支え手の有無で決まる」（調査クロス集計・分析 17シート）</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>施設志向群と在宅志向群で困りごと・移動制約・経済状況・フレイルに有意差がないことを根拠としているが、「有意差がない」ことは「関係がない」ことを意味しない。標本規模による検出力を検討していない。</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>検出力が不足している場合、実際には差があっても有意にならない。分母は施設志向1,418人・在宅志向2,251人であり検出力は高いが、示すべきは検出力ではなく効果量の小ささである。</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>「支え手の有無と強く結びついている」に改める。有意差がない項目については差の大きさと信頼区間を併記する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="140" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>「朗根内地区は訪問・通所困難地域に該当する可能性が最も高い」（素案 第1章第7節）</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>人口233人、スクールバス依存、除雪率52.9％の組合せからの推論であり、判定基準として自ら定義した「事業所の通常の事業の実施地域」を確認していない。判定の根拠そのものが未取得である。</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>朗根内地区が複数の事業所の実施地域に含まれていれば、困難地域には該当しない。逆に、より人口の多い地区が実施地域から外れている可能性もある。</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>推量の形は維持しつつ、「判定の根拠となる実施地域を確認していない」ことを明記する（不足資料No.2）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="140" customHeight="1">
+      <c r="A14" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>「第9期の人口推計は分母（総人口）の過大が原因で高齢化率が低い」（妥当性検証 03シート）</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>高齢化率の差を分母の過大で説明しているが、第9期計画と見える化の65歳以上人口はほぼ一致しており分母の差が主因であることは示せる一方、「原因」という語は要因の特定を意味する。分母の差が生じた理由（住基と国勢調査の基準差、社会増の見込み）は特定していない。</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>分母の差が住基と国勢調査の基準差によるものであれば、推計の誤りではなく基準の違いである。社会増の見込みの過大であれば推計の見直しを要する。対応が正反対になる。</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>「高齢化率が低くなるのは、65歳以上人口がほぼ一致する一方で総人口が大きいためである」に改める。町別人口の実績により検証する（不足資料No.3）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="140" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>「訪問介護の高い利用強度は通所の供給が薄いことによる代替である」（素案 第2章第2節）</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>訪問介護1.87倍と通所0.74倍という2つの比率の対比からの推論であり、同一利用者における訪問と通所の組合せを確認していない。現在も推量の形で記述しているが、推量の根拠が2つの比率の対比のみであることを示していない。</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>訪問介護の利用者と通所介護の利用者が別の層であれば、代替関係は成り立たない。世帯構成や移動制約により訪問を選択している可能性もある。</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>「代替の可能性がある」の根拠が2つの比率の対比にとどまることを明記する。ケアプランのサービス構成により検証する（不足資料No.8）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="140" customHeight="1">
+      <c r="A16" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>自給率と給付水準の関係について、外れ値に駆動された相関を示しかけた（地域差の分析06シートの検討過程）</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>単一市町村保険者19件で相関を計算するとr＝0.53となり「自給率が低いほど給付水準が高い」という関係が見えるが、これは自給率0.0％の2村（占冠村0.82・音威子府村0.73）による。この2村を除く15件ではr＝0.07で無相関となる。</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>外れ値を含めたまま相関を報告すれば、区域外利用が給付水準を押し上げているという誤った結論に至る。自給率0.0％は区域内に事業所が存在しないことを示し、指標として他と性質が異なる。</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>本表では両方の値を示し、除外の理由を明記した。今後、相関を報告する際は外れ値の有無による感度を必ず併記する。記述ルール（主張の根拠水準の棚卸し07シート）に追加する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>注1）No.7・No.8・No.10は、いずれも「同じ事実から逆の政策的含意が導かれうる」性質の指摘である。供給が足りないのか需要が少ないのか、施設に入れないのか在宅を選んでいるのかで、第10期の整備方針が変わる。注2）これらの区別には、区域内外の利用の別、未利用認定者の要因別内訳、本人・家族の意向が必要である。調査クロス集計・分析15シートで意向の一部は把握したが、給付側の情報（確認No.23・30）が不足している。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A18:F18"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2091,14 +2971,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>データと出典への指摘</t>
+          <t>評価の枠組みへの指摘</t>
         </is>
       </c>
     </row>
     <row r="2" ht="56" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>用いたデータの時点、範囲、確定性に関する指摘。評価しようとしている期間のデータを使っているか、結論を支えるために必要な系列が揃っているか、概算値を確定値のように扱っていないかを点検した。</t>
+          <t>評価の範囲、比較対象の選定、保険者の自己評価との関係、反証可能性に関する指摘。個々のデータや推論ではなく、評価そのものの設計を点検した。</t>
         </is>
       </c>
     </row>
@@ -2136,7 +3016,7 @@
     </row>
     <row r="5" ht="140" customHeight="1">
       <c r="A5" s="4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
@@ -2145,58 +3025,58 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>「年齢層をそろえると認定率は低下している」（妥当性検証 所見7、素案 第3章第4節）</t>
+          <t>本評価を「第9期計画の評価・検証」と称している（妥当性検証報告書全体、素案 第3章）</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>根拠としているのは合計認定率・75歳以上・85歳以上の3系列のみで、65〜74歳の認定率を確認していない。75歳以上という括りの内部でも75〜84歳と85歳以上の構成比が変化しているため、75歳以上の粗率は依然として年齢構成の影響を受ける。真の年齢調整（5歳階級別の直接法）は行っていない。</t>
+          <t>評価の中心は①代表KPIの達成度②指標設計の妥当性③交付金による外部評価であり、最も基本的な「計画に位置づけた事業が計画どおり実施されたか」というプロセス評価が、実績未受領のため空白のままである。この状態で「評価・検証」と称するのは範囲の誇張にあたる。</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>65〜74歳の認定率が上昇していれば、「全年齢層で低下」という主張は崩れる。また、性・年齢調整済み要介護2以上認定率（W144）は9.25％で全国を上回り、変化率も＋1.76と悪化している。調整済みの指標が悪化しているのに「調整すると低下」と述べるのは、少なくとも説明が不足している。</t>
+          <t>委員会や北海道から「実績を見ずに何を評価したのか」と問われうる。評価の3分の1程度しか行えていない状態である。</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>見える化B4系列の年齢階級別認定率（65〜74歳を含む）を取得し、5歳階級別の直接法により再計算する。W144との整合を「軽度は改善・中重度は悪化」で説明するのであれば、要介護度別の認定率の推移でそれを実証する。</t>
+          <t>現時点の成果物の表題を「第9期計画の評価・検証（中間・記載事項の検証）」とし、実績に基づく評価は別に行うことを明記する。業務工程管理表の(2)の進捗0.80は、この空白を踏まえると過大の可能性がある。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="140" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>重大</t>
+        <v>14</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>交付金の評価得点を「第9期の評価」として用いている（妥当性検証 所見18・19、保険料と施策評価の他団体比較 04シート）</t>
+          <t>比較対象（他団体）の選定</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>用いたのは令和5年調査（令和6年度分指標）である。調査は令和5年度に実施され、評価対象は主に令和4年度の実施状況である。第9期は令和6年度からであるから、この得点は第9期の取組をほとんど反映していない。実質的には第8期の評価である。</t>
+          <t>同規模保険者40はJAGESの参加団体であって介護保険上の類似保険者ではない。上川管内21保険者は地理的近接で選んだものである。「類似保険者」の定義を先に決めずに、入手できたデータで比較しているため、事後的な選定になっている。</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>「活動指標群が全国の23.2％」は第8期末の記録・報告体制を示すものであり、第9期に改善している可能性を排除できない。第9期の評価としてこれを用いると、保険者の第9期の努力を不当に低く評価することになる。</t>
+          <t>都合の良い比較対象を選んだと見られうる。特に「同規模保険者と同等」「全国を上回る」といった評価は、比較対象が変われば結論が変わる。</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>令和6年調査・令和7年調査（令和7年度分・令和8年度分指標）の得点を取得し、経年で比較する。取得できない場合は、「第8期の取組を反映した評価である」と明記して用いる。</t>
+          <t>類似保険者の選定条件（人口規模・高齢化率・施設整備状況・財政力等）を先に決定する（確認No.3）。現在の比較は「入手可能な比較対象による暫定的なもの」と位置づける。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="140" customHeight="1">
       <c r="A7" s="4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
@@ -2205,28 +3085,28 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>「第9期は2年で約42百万円の剰余が生じている」（妥当性検証 所見9、素案 第6章第6節）</t>
+          <t>保険者の自己評価との関係が整理されていない</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>必要保険料月額（見える化P4）と条例基準額の差に被保険者数と12月を乗じた概算である。令和6年度の値は令和8年1月時点の実績を年度換算したものであり、確定値ではない。決算及び基金の積立実績で確認していない。</t>
+          <t>介護保険法第117条は計画の実績に関する評価と公表を求めている。第9期に保険者自身が自己評価を行っていたかを確認しないまま（確認No.7）、受託者が外部から評価を行っている。</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>年度末までの給付費の変動、地域支援事業費の執行残、国庫負担金の精算等により、決算ベースの剰余は概算と大きく異なりうる。42百万円という具体的な金額を示すと、決算と食い違ったときに評価全体の信頼を損なう。</t>
+          <t>保険者の自己評価が存在する場合、本評価との相違点を説明する必要がある。相違があるまま計画に載せると、保険者の見解と受託者の見解が並立することになる。</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>「概算」であることを金額の直後に明記する。決算書及び基金の積立・取崩実績を受領し、確定値に置き換える（確認No.16）。</t>
+          <t>第9期の自己評価の有無と内容を確認する（確認No.7）。存在する場合は本評価との対照表を作成する。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="140" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
@@ -2235,149 +3115,149 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>第7期の保険料基準額を6,077円に訂正した（保険料と施策評価の他団体比較 02シート、素案 第6章第6節）</t>
+          <t>小規模保険者であることを考慮しない比較</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>訂正の根拠は「剰余の累計＋159円／月と整合するのは6,077円だけである」という内部整合性のみで、条例で確認していない。＋159円という数字自体が誤っていれば、訂正が誤りとなる。</t>
+          <t>交付金の得点を全国平均と比較して「78.6％」と評価しているが、評価項目には職員体制や実施件数を問うものが含まれ、小規模保険者は構造的に不利である。人口規模を揃えた比較になっていない。</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>＋159円の出所は第9稿の記載であり、その根拠も未確認である。6,077円と5,900円のいずれかが正しいのではなく、両方が誤っている可能性もある。</t>
+          <t>「保険者の努力不足」と読まれるが、実際には職員数の制約による可能性がある。3町・広域連合の職員体制を踏まえない評価は実務者の納得を得にくい。</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>第7期（平成30〜令和2年度）の保険料条例により確認する（確認No.32）。確認できるまで、素案には両論を併記するか、記載を保留する。</t>
+          <t>交付金の得点を人口規模別に比較できるデータの有無を確認する。得られない場合は、規模の制約を注記したうえで、0点項目のうち規模によらず実施可能なものを特定する。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="140" customHeight="1">
       <c r="A9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>中</t>
+        <v>17</v>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>軽微</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>「3町の高齢者福祉計画に数値目標が1件も設定されていない」（妥当性検証 所見5）</t>
+          <t>判定基準が資料により異なる</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>判定の根拠は「数値目標」「目標値」という語の全文検索による出現回数である。語が使われていなくても、表や本文に実質的な目標値が示されている可能性を排除していない。</t>
+          <t>同規模保険者との比較（19シート）は差1.0ポイントを閾値としているが、他のシートの「妥当」「課題」の判定は定性的である。統一した基準がない。</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>3町の計画に「○年度までに△件」のような記述が、「数値目標」という語を使わずに含まれている場合、判定は誤りとなる。3町に対して「目標が1件もない」と断じることは関係上の影響も大きい。</t>
+          <t>判定が恣意的であるとの批判を受けうる。</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>3町の計画の各章を目視で確認し、数値を伴う記述の有無を再点検する。そのうえで「進行管理の対象として明示された数値目標がない」等、判定の範囲を限定した表現に改める。</t>
+          <t>判定基準を成果物間で統一し、各表の注に明記する。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="140" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>軽微</t>
+        <v>18</v>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>重大</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>認定率の実績を「令和8年3月末21.8％」と表記している（妥当性検証 02シート）</t>
+          <t>反証条件が示されていない</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>令和8年3月末は令和7年度末である。第9期は令和6〜8年度であるから、最終年度（令和8年度）の実績はまだ出ていない。現時点の評価は中間評価であって、期の評価ではない。</t>
+          <t>主要所見20件のいずれについても、「どのようなデータが得られれば、この所見は誤りだったと分かるか」を示していない。検証可能な形で提示されていない。</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>「令和8年3月末」という表記は、令和8年度末と読まれるおそれがある。</t>
+          <t>所見が反証不可能な形で提示されていると、評価としての質が担保されない。第10期の年次評価で見直す仕組みも働かない。</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>「令和7年度末（令和8年3月末）」と年度を明記する。第9期の最終評価は令和9年3月末の実績によることを明示する。</t>
+          <t>主要所見ごとに反証条件を明示する（06シート）。第10期の年次PDCAで、反証条件に照らして所見を見直す。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="140" customHeight="1">
       <c r="A11" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>重大</t>
+        <v>25</v>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>軽微</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>「交付金の得点は第8期の取組を反映している」（複数の成果物）</t>
+          <t>「本分析の値は調査報告書の公表値と完全に一致する」（調査クロス集計・分析 00・14シート）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>No.2の指摘を受けて加えた限定であるが、その限定自体が調査の実施年度と交付年度の関係からの推論であり、調査要領で評価対象期間を直接確認していない。評価項目により対象期間が異なる可能性がある（体制は調査時点、活動は前年度実績など）。</t>
+          <t>一致を確認したのは広域連合全体及び町別の主要指標であり、全設問について確認したわけではない。確認の範囲を示さずに「完全に一致」と記述している。</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>評価項目ごとに対象期間が異なる場合、「第8期の取組を反映している」という一律の説明は成り立たない。指摘への対応として加えた説明が、それ自体新たな未検証の断定になっている。</t>
+          <t>確認していない設問で不一致がある可能性を排除できない。個票データの再現性の主張が過大になる。</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>「令和5年度に実施された調査であり、第9期（令和6年度〜）の取組は反映されていない」という確認できる範囲の限定に改める。評価調書及び調査要領で確認する（不足資料No.5）。</t>
+          <t>「広域連合全体及び町別の主要20指標について一致を確認した」に改め、確認した指標名を注記する。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="140" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>軽微</t>
+        <v>28</v>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>重大</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>国標準13段階の乗率を介護保険法施行令の内容として記述している（保険料の所得段階と低所得者軽減の検証 02シート）</t>
+          <t>給付水準を全国比のみで評価し、管内の位置を確認していなかった（妥当性検証 所見1・2、素案 第2章第2節・第3章）</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>施行令の条文を直接確認しておらず、複数の自治体公表資料により確認したものである。出典の水準が原典ではない。</t>
+          <t>給付月額指数1.08を「全国を8％上回る」として第9期の課題としてきたが、上川管内21保険者のなかでは8〜10位（比布町・剣淵町と同値）であり、管内中位値1.05に近い。管内には愛別町1.23、中川町1.21がある。さらに平成21年度の給付月額21,490円は管内1位であり、令和7年度26,885円は12位で管内中位値26,892円とほぼ同値である。17年間の伸び率＋25.1％は管内16位で、管内平均＋46.4％を大きく下回る。</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>自治体の資料に誤りがある可能性は低いが、出典として施行令を示すのであれば条文の確認を要する。</t>
+          <t>給付水準の高さは平成21年度から続く構造であり、第9期に生じた変化ではない。かつ伸びは管内で最も抑制されている側に属する。「給付水準が高いことが第9期の課題である」という枠組みは、長期の改善を見落としている。</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>出典を「介護保険法施行令第38条・第39条（複数の自治体公表資料により確認）」と明記する。第10期の標準乗率は政令改正により定まる（不足資料No.11）。</t>
+          <t>第9期の評価に管内の位置と長期の推移を加える。「水準は全国を上回るが、管内では平均並みであり、17年間の伸びは管内で小さい」という両面の記述に改める（地域差の分析13シート）。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>注1）No.1（年齢調整）とNo.2（交付金の時点）は、いずれも「評価の結論が逆になりうる」性質の指摘である。No.1は調整済み指標（W144）が悪化していることと矛盾し、No.2は評価対象期間そのものがずれている。注2）No.3・No.4は金額・水準の確定性に関する指摘である。概算値であることを明記すれば足りるが、具体的な金額を示している以上、確定値による置換えが望ましい。</t>
+          <t>注1）No.13は本レビューで最も重い指摘である。第9期の評価のうち、事業が計画どおり実施されたかというプロセス評価が実績未受領のため空白であり、現状は「計画の記載事項の検証」と「外部評価の分析」にとどまる。成果物の表題と業務工程管理表の進捗の表現を改める必要がある。注2）No.16は、指摘が正しくても評価そのものは変わらないが、3町・広域連合の実務者の納得を得るために不可欠な視点である。</t>
         </is>
       </c>
     </row>
@@ -2385,706 +3265,6 @@
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>推論への指摘</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="56" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>データから結論を導く過程に関する指摘。同じ事実を説明できる別の仮説、特に逆の政策的含意をもつ仮説を併記した。因果の方向を特定できているかも点検した。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>重大度</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>対象となる主張</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>指摘（成り立たない可能性）</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>別の説明・想定される反論</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>対応</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="140" customHeight="1">
-      <c r="A5" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>重大</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>「給付水準の高さは施設・居住系サービスの受給率に集約される」（妥当性検証 所見1）</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>地域差指数を認定率・受給率・単価に分解しているが、これらは独立ではない。施設が多ければ受給率も単価も同時に上がるため、「受給率に集約される」という表現は要因の特定になっていない。また、因果の方向（施設があるから給付が高い／需要があるから施設がある）を特定していない。</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>介護老人福祉施設の定員が234人から160人へ減少しているにもかかわらず施設・居住系の受給率が高いという事実は、この説明と緊張関係にある。区域外施設の利用（住所地特例を含む）が多いことによる可能性があり、その場合、区域内の整備方針を論じる根拠にはならない。</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>区域内施設の利用者数と区域外施設の利用者数を分けて把握する。自給率（δ2・δ3）の算定（国保連の給付実績情報と指定事業所台帳の突合）により検証する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="140" customHeight="1">
-      <c r="A6" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>重大</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>「介護サービス利用率の低下は供給制約による」という含意（妥当性検証 所見2、素案 第2章第2節3）</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>認定者が増え受給者が減ったという事実だけでは、供給制約は導けない。未利用の理由には、軽度で自立している、申請だけ先行した、家族介護で足りている、経済的理由、供給がない、が並立する。素案では要因分解の必要性を書いているが、他の資料では「課題」として断定的に扱っている箇所がある。</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>第9期に認定を受けやすくする働きかけ（申請勧奨）を行った結果として認定者が増え、そのうち軽度者が利用に至っていないだけであれば、供給制約ではなく認定行政の変化である。この場合、施策の方向は逆になる。</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>居宅サービス計画未作成者の要介護度別内訳を把握する。新規認定者数と認定申請件数の推移を確認する。断定的な表現を「要因の分解を要する」に統一する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="140" customHeight="1">
-      <c r="A7" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>重大</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>「成果は全国トップ級」（妥当性検証 所見19、保険料と施策評価の他団体比較 04・05シート）</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>成果指標（目標Ⅳ）は要介護度の変化率であり、認定者約1,960人という母集団では単年度の変動が大きい。統計的な安定性を検証していない。また、長期指標が良好である一方、直近の変化率は全国と逆方向に悪化している。</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>少数の重度化事例の増減で指標が大きく振れる。「全国の0.51倍」という値は、実数でみれば数十人規模の差にすぎない可能性がある。「トップ級」という表現は一時点の結果を過大に評価している。</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>目標Ⅳの各指標の分子・分母の実数を確認する。複数年の推移でみたうえで、「全国トップ級」という表現を「令和6年度分指標では全国を上回る」に改める。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="140" customHeight="1">
-      <c r="A8" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>「重度者の在宅化が進む」（妥当性検証 所見3）</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>要介護5の在宅・居住系割合が31.3％から54.6％へ上昇したことを「在宅化」と表現しているが、施設に入れないから在宅にいるのか、在宅を支える体制ができたから在宅にいるのかで意味が正反対になる。この区別を論証していない。</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>24時間対応の3サービスが区域内に存在しないことを考えると、在宅を支える体制がない中で在宅にとどまっている、すなわち家族介護への転嫁である可能性が高い。「在宅化が進む」という表現は、政策の成果と誤読されうる。</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>「施設定員の縮小と同時に進んでおり、在宅の支援体制が整った結果ではない」と明記する。本人・家族の状況（調査クロス集計・分析 15シート）と併せて記述する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="140" customHeight="1">
-      <c r="A9" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>施策の「評価可能性」判定（部分評価6施策・指標不足13施策）（施策体系新旧対照表 施策の新旧対照）</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>計画文書の記載のみによる机上評価であり、事業が実際に行われたか、効果があったかは一切見ていない。「指標不足」は計画の記載の問題であって、施策の良否ではない。</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>指標が計画に書かれていなくても、事業として実施され成果を上げている可能性がある。19施策のうち13を「指標不足」と示すと、施策そのものが不十分であったと受け取られるおそれがある。</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>「計画記載上の評価可能性」であることを表題と注に明記する。令和6〜8年度の事業実績（確認No.5）を受領後、実施状況の評価を別に行う。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="140" customHeight="1">
-      <c r="A10" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>東川町の人口推計が「社人研から大きく上振れしている」（妥当性検証 所見4）</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>第9期計画は住民基本台帳ベース、社人研は国勢調査ベースであり、基準そのものが異なる。美瑛町の乖離（＋2.2〜3.2％）は「住基と国勢調査の基準差」と説明しているのに、東川町の＋18.5％だけを「上振れ」と断じており、基準差と社会増の分離ができていない。</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>東川町は移住施策により実際に社会増が続いている可能性があり、その場合は社人研推計が過小である。どちらが正しいかを検証せずに「上振れ」と評価するのは片側に寄っている。</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>令和6年・令和7年の住民基本台帳実績を両推計に当てはめ、どちらが実績に近いかを検証する。そのうえで第10期の人口推計の基礎とする系列を決定する（確認No.14）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="140" customHeight="1">
-      <c r="A11" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>重大</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>「受給率の低下分のほぼ全てが要介護5に由来する」（妥当性検証 13シート）</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>要介護度別の受給率の推移から低下分の帰属を述べているが、要介護5の受給者が減った理由を特定していない。死亡、施設入所、認定の変化、区域外への転出が並立する。「由来する」は要因の特定を意味する語であり、差の帰属の計算とは別のものである。</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>要介護5の受給者の減少が死亡によるものであれば、サービス供給の問題ではなく人口動態の問題である。この場合、第10期の整備方針の根拠にはならない。</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>「低下分の大半は要介護5の受給率の低下による」に改める。要因の特定には認定・給付データを要する（不足資料No.8）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="140" customHeight="1">
-      <c r="A12" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>「施設入所志向は心身の状態や経済状況ではなく支え手の有無で決まる」（調査クロス集計・分析 17シート）</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>施設志向群と在宅志向群で困りごと・移動制約・経済状況・フレイルに有意差がないことを根拠としているが、「有意差がない」ことは「関係がない」ことを意味しない。標本規模による検出力を検討していない。</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>検出力が不足している場合、実際には差があっても有意にならない。分母は施設志向1,418人・在宅志向2,251人であり検出力は高いが、示すべきは検出力ではなく効果量の小ささである。</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>「支え手の有無と強く結びついている」に改める。有意差がない項目については差の大きさと信頼区間を併記する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="140" customHeight="1">
-      <c r="A13" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>「朗根内地区は訪問・通所困難地域に該当する可能性が最も高い」（素案 第1章第7節）</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>人口233人、スクールバス依存、除雪率52.9％の組合せからの推論であり、判定基準として自ら定義した「事業所の通常の事業の実施地域」を確認していない。判定の根拠そのものが未取得である。</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>朗根内地区が複数の事業所の実施地域に含まれていれば、困難地域には該当しない。逆に、より人口の多い地区が実施地域から外れている可能性もある。</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>推量の形は維持しつつ、「判定の根拠となる実施地域を確認していない」ことを明記する（不足資料No.2）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="140" customHeight="1">
-      <c r="A14" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>「第9期の人口推計は分母（総人口）の過大が原因で高齢化率が低い」（妥当性検証 03シート）</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>高齢化率の差を分母の過大で説明しているが、第9期計画と見える化の65歳以上人口はほぼ一致しており分母の差が主因であることは示せる一方、「原因」という語は要因の特定を意味する。分母の差が生じた理由（住基と国勢調査の基準差、社会増の見込み）は特定していない。</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>分母の差が住基と国勢調査の基準差によるものであれば、推計の誤りではなく基準の違いである。社会増の見込みの過大であれば推計の見直しを要する。対応が正反対になる。</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>「高齢化率が低くなるのは、65歳以上人口がほぼ一致する一方で総人口が大きいためである」に改める。町別人口の実績により検証する（不足資料No.3）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="140" customHeight="1">
-      <c r="A15" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>「訪問介護の高い利用強度は通所の供給が薄いことによる代替である」（素案 第2章第2節）</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>訪問介護1.87倍と通所0.74倍という2つの比率の対比からの推論であり、同一利用者における訪問と通所の組合せを確認していない。現在も推量の形で記述しているが、推量の根拠が2つの比率の対比のみであることを示していない。</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>訪問介護の利用者と通所介護の利用者が別の層であれば、代替関係は成り立たない。世帯構成や移動制約により訪問を選択している可能性もある。</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>「代替の可能性がある」の根拠が2つの比率の対比にとどまることを明記する。ケアプランのサービス構成により検証する（不足資料No.8）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>注1）No.7・No.8・No.10は、いずれも「同じ事実から逆の政策的含意が導かれうる」性質の指摘である。供給が足りないのか需要が少ないのか、施設に入れないのか在宅を選んでいるのかで、第10期の整備方針が変わる。注2）これらの区別には、区域内外の利用の別、未利用認定者の要因別内訳、本人・家族の意向が必要である。調査クロス集計・分析15シートで意向の一部は把握したが、給付側の情報（確認No.23・30）が不足している。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A17:F17"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>評価の枠組みへの指摘</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="56" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>評価の範囲、比較対象の選定、保険者の自己評価との関係、反証可能性に関する指摘。個々のデータや推論ではなく、評価そのものの設計を点検した。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>重大度</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>対象となる主張</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>指摘（成り立たない可能性）</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>別の説明・想定される反論</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>対応</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="140" customHeight="1">
-      <c r="A5" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>重大</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>本評価を「第9期計画の評価・検証」と称している（妥当性検証報告書全体、素案 第3章）</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>評価の中心は①代表KPIの達成度②指標設計の妥当性③交付金による外部評価であり、最も基本的な「計画に位置づけた事業が計画どおり実施されたか」というプロセス評価が、実績未受領のため空白のままである。この状態で「評価・検証」と称するのは範囲の誇張にあたる。</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>委員会や北海道から「実績を見ずに何を評価したのか」と問われうる。評価の3分の1程度しか行えていない状態である。</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>現時点の成果物の表題を「第9期計画の評価・検証（中間・記載事項の検証）」とし、実績に基づく評価は別に行うことを明記する。業務工程管理表の(2)の進捗0.80は、この空白を踏まえると過大の可能性がある。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="140" customHeight="1">
-      <c r="A6" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>比較対象（他団体）の選定</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>同規模保険者40はJAGESの参加団体であって介護保険上の類似保険者ではない。上川管内21保険者は地理的近接で選んだものである。「類似保険者」の定義を先に決めずに、入手できたデータで比較しているため、事後的な選定になっている。</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>都合の良い比較対象を選んだと見られうる。特に「同規模保険者と同等」「全国を上回る」といった評価は、比較対象が変われば結論が変わる。</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>類似保険者の選定条件（人口規模・高齢化率・施設整備状況・財政力等）を先に決定する（確認No.3）。現在の比較は「入手可能な比較対象による暫定的なもの」と位置づける。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="140" customHeight="1">
-      <c r="A7" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>保険者の自己評価との関係が整理されていない</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>介護保険法第117条は計画の実績に関する評価と公表を求めている。第9期に保険者自身が自己評価を行っていたかを確認しないまま（確認No.7）、受託者が外部から評価を行っている。</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>保険者の自己評価が存在する場合、本評価との相違点を説明する必要がある。相違があるまま計画に載せると、保険者の見解と受託者の見解が並立することになる。</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>第9期の自己評価の有無と内容を確認する（確認No.7）。存在する場合は本評価との対照表を作成する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="140" customHeight="1">
-      <c r="A8" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>小規模保険者であることを考慮しない比較</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>交付金の得点を全国平均と比較して「78.6％」と評価しているが、評価項目には職員体制や実施件数を問うものが含まれ、小規模保険者は構造的に不利である。人口規模を揃えた比較になっていない。</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>「保険者の努力不足」と読まれるが、実際には職員数の制約による可能性がある。3町・広域連合の職員体制を踏まえない評価は実務者の納得を得にくい。</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>交付金の得点を人口規模別に比較できるデータの有無を確認する。得られない場合は、規模の制約を注記したうえで、0点項目のうち規模によらず実施可能なものを特定する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="140" customHeight="1">
-      <c r="A9" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>軽微</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>判定基準が資料により異なる</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>同規模保険者との比較（19シート）は差1.0ポイントを閾値としているが、他のシートの「妥当」「課題」の判定は定性的である。統一した基準がない。</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>判定が恣意的であるとの批判を受けうる。</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>判定基準を成果物間で統一し、各表の注に明記する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="140" customHeight="1">
-      <c r="A10" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>重大</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>反証条件が示されていない</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>主要所見20件のいずれについても、「どのようなデータが得られれば、この所見は誤りだったと分かるか」を示していない。検証可能な形で提示されていない。</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>所見が反証不可能な形で提示されていると、評価としての質が担保されない。第10期の年次評価で見直す仕組みも働かない。</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>主要所見ごとに反証条件を明示する（06シート）。第10期の年次PDCAで、反証条件に照らして所見を見直す。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="140" customHeight="1">
-      <c r="A11" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>軽微</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>「本分析の値は調査報告書の公表値と完全に一致する」（調査クロス集計・分析 00・14シート）</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>一致を確認したのは広域連合全体及び町別の主要指標であり、全設問について確認したわけではない。確認の範囲を示さずに「完全に一致」と記述している。</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>確認していない設問で不一致がある可能性を排除できない。個票データの再現性の主張が過大になる。</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>「広域連合全体及び町別の主要20指標について一致を確認した」に改め、確認した指標名を注記する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>注1）No.13は本レビューで最も重い指摘である。第9期の評価のうち、事業が計画どおり実施されたかというプロセス評価が実績未受領のため空白であり、現状は「計画の記載事項の検証」と「外部評価の分析」にとどまる。成果物の表題と業務工程管理表の進捗の表現を改める必要がある。注2）No.16は、指摘が正しくても評価そのものは変わらないが、3町・広域連合の実務者の納得を得るために不可欠な視点である。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3862,7 +4042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3884,7 +4064,7 @@
     <row r="2" ht="56" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26件の指摘について、記述の修正・追加分析・確認事項のいずれで対応するかを整理する。追加のデータがなくても対応できるものと、資料の受領を要するものを区別する。</t>
+          <t>29件の指摘について、記述の修正・追加分析・確認事項のいずれで対応するかを整理する。追加のデータがなくても対応できるものと、資料の受領を要するものを区別する。</t>
         </is>
       </c>
     </row>
@@ -4802,140 +4982,245 @@
     </row>
     <row r="30" ht="64" customHeight="1">
       <c r="A30" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>地域差指数の3要素の分解を要因の按分に用いていた</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>記述の修正</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>出典を「施行令第38条・第39条（複数の自治体公表資料により確認）」と明記する</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>介護保険法施行令（不足資料No.11）</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="64" customHeight="1">
+      <c r="A31" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>給付水準を全国比のみで評価し、管内の位置を確認していなかった</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>記述の修正＋追加分析</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>分解による按分の記述を撤回し、4要素を並列の指標として示す。要因の特定は管内21保険者の回帰による</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>D49の指標定義（不足資料No.16）</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="64" customHeight="1">
+      <c r="A32" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>自給率と給付水準の関係について、外れ値に駆動された相関を示しかけた</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>記述の修正＋追加分析</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>第9期の評価に管内の位置と長期の推移を加え、「水準は全国を上回るが管内では平均並み、伸びは管内で小さい」に改める</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>―（見える化C1により実施済）</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>軽微</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>国標準13段階の乗率を介護保険法施行令の内容として記述している</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr">
+      <c r="D33" s="20" t="inlineStr">
         <is>
           <t>記述の修正</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>出典を「施行令第38条・第39条（複数の自治体公表資料により確認）」と明記する</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>介護保険法施行令（不足資料No.11）</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>相関を報告する際は外れ値の有無による感度を併記する。記述ルールに追加する</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>【対応の集計】</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="32" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr"/>
-      <c r="G33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34" ht="44" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr"/>
+      <c r="E36" s="3" t="inlineStr"/>
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="44" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>記述の修正により対応できる</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n">
-        <v>19</v>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="B37" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>記述の修正・表現の限定・注記の追加により対応する。計画素案の次稿で反映する。再レビューの8件（No.19〜26）を含む</t>
         </is>
       </c>
-      <c r="D34" s="7" t="n"/>
-      <c r="E34" s="7" t="n"/>
-      <c r="F34" s="7" t="n"/>
-      <c r="G34" s="8" t="n"/>
-    </row>
-    <row r="35" ht="44" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="n"/>
+      <c r="G37" s="8" t="n"/>
+    </row>
+    <row r="38" ht="44" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>受領済の資料で対応できる</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n">
+      <c r="B38" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>3町の計画の再点検（No.5）、反証条件の明示（No.18・実施済）</t>
         </is>
       </c>
-      <c r="D35" s="7" t="n"/>
-      <c r="E35" s="7" t="n"/>
-      <c r="F35" s="7" t="n"/>
-      <c r="G35" s="8" t="n"/>
-    </row>
-    <row r="36" ht="44" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="D38" s="7" t="n"/>
+      <c r="E38" s="7" t="n"/>
+      <c r="F38" s="7" t="n"/>
+      <c r="G38" s="8" t="n"/>
+    </row>
+    <row r="39" ht="44" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>資料の受領を要する</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n">
+      <c r="B39" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>No.1（見える化B4系列）・No.3（決算・基金）・No.4（条例）・No.12（町別人口実績）・No.15（自己評価）</t>
         </is>
       </c>
-      <c r="D36" s="7" t="n"/>
-      <c r="E36" s="7" t="n"/>
-      <c r="F36" s="7" t="n"/>
-      <c r="G36" s="8" t="n"/>
-    </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>注1）26件のうち19件は記述の修正により対応できる。記述の限定と注記の追加により、評価の結論を変えずに信頼性を高めることができる。注2）最も優先すべきはNo.1（年齢調整）とNo.13（評価範囲）である。No.1は見える化B4系列の取得により検証でき、No.13は表題と進捗の表現の見直しで足りる。注3）本レビューの指摘は、業務工程管理表の確認事項一覧に反映する。</t>
+      <c r="D39" s="7" t="n"/>
+      <c r="E39" s="7" t="n"/>
+      <c r="F39" s="7" t="n"/>
+      <c r="G39" s="8" t="n"/>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>注1）大半の指摘は記述の修正により対応できる。記述の限定と注記の追加により、評価の結論を変えずに信頼性を高めることができる。注2）最も優先すべきはNo.1（年齢調整）とNo.13（評価範囲）である。No.1は見える化B4系列の取得により検証でき、No.13は表題と進捗の表現の見直しで足りる。注3）本レビューの指摘は、業務工程管理表の確認事項一覧に反映する。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="C35:G35"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="C37:G37"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C39:G39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4947,7 +5232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5800,99 +6085,137 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="31" ht="76" customHeight="1">
+      <c r="A31" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>地域差指数の分解を按分に用いていた</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>訂正（指摘的中）</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>上川管内21保険者について検証したところ、受給率×受給者単価は給付月額指数に一致せず、16保険者で0.03を超えてずれることが判明した（大雪＋0.065）。分解による按分の記述を撤回し、管内の分散を説明する要素（受給者単価R²＝0.62、受給率0.45、認定率0.35）を示す方法に改めた。</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>地域差の分析 04・05シート
+主張の根拠水準の棚卸し C1・C2・C7</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="76" customHeight="1">
+      <c r="A32" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>全国比のみで評価し管内の位置を見ていなかった</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>訂正（指摘的中）</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>見える化C1・D49により管内の位置を確認したところ、給付月額指数1.08は管内8〜10位で中位値1.05に近く、平成21年度は管内1位であった給付月額が令和7年度は12位、17年間の伸び率＋25.1％は管内16位（管内平均＋46.4％）であった。第9期の評価に管内の位置と長期の推移を加える。</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>地域差の分析 03・13シート
+主張の根拠水準の棚卸し C6・C8</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="76" customHeight="1">
+      <c r="A33" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>外れ値に駆動された相関</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>自給率と給付月額指数の相関について、自給率0.0％の2村を含めるとr＝0.53、除くとr＝0.07となることを示し、除外の理由を明記した。相関を報告する際の感度の併記を記述ルールに追加する。</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>地域差の分析 06シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>【対応状況の集計】</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="32" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>対応済</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>記述の修正・表現の限定・注記の追加を実施した</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="n"/>
-      <c r="E34" s="7" t="n"/>
-      <c r="F34" s="8" t="n"/>
-    </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>対応中</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>No.19〜No.26。令和8年7月29日の再レビューで新たに特定した指摘であり、改める記述を確定したうえで各成果物に反映する</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="n"/>
-      <c r="E35" s="7" t="n"/>
-      <c r="F35" s="8" t="n"/>
-    </row>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>訂正（指摘的中）</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>No.5（3町の数値目標）とNo.1（年齢調整）。いずれも指摘が的中し、評価の記述を訂正した。特にNo.1では「軽度は改善・中重度は悪化」という従来の説明が逆であることが判明し、施策の重点に影響する</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="n"/>
-      <c r="E36" s="7" t="n"/>
-      <c r="F36" s="8" t="n"/>
+      <c r="D36" s="3" t="inlineStr"/>
+      <c r="E36" s="3" t="inlineStr"/>
+      <c r="F36" s="3" t="inlineStr"/>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>対応済（確認待ち）</t>
+          <t>対応済</t>
         </is>
       </c>
       <c r="B37" s="16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>No.4。注記済みで、条例による確認を依頼済み</t>
+          <t>記述の修正・表現の限定・注記の追加を実施した</t>
         </is>
       </c>
       <c r="D37" s="7" t="n"/>
@@ -5902,39 +6225,112 @@
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>未対応（資料待ち）</t>
+          <t>対応中</t>
         </is>
       </c>
       <c r="B38" s="16" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>No.12・No.15。いずれも確認事項として依頼済み</t>
+          <t>No.19〜No.26及びNo.29。再レビューで新たに特定した指摘であり、改める記述を確定したうえで各成果物に反映する</t>
         </is>
       </c>
       <c r="D38" s="7" t="n"/>
       <c r="E38" s="7" t="n"/>
       <c r="F38" s="8" t="n"/>
     </row>
-    <row r="40" ht="84" customHeight="1">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t>注1）No.5は本レビューの指摘が的中し、評価の結論そのものを訂正した事例である。「3町の高齢者福祉計画に数値目標が1件も設定されていない」という所見は誤りであり、東川町は令和6〜8年度を対象とする事業の数値目標を6事業10項目以上設定していた。検索語に依存した判定の危うさが実証された。注2）この訂正は第10期にとって前向きな材料でもある。東川町には事業の数値目標を年度別に設定し実績と対比する仕組みが既にあるため、第10期の共通指標の掲載は同町では実現可能性が高く、美瑛町・東神楽町にはその様式を参考として示すことができる。注3）No.1も指摘が的中した。見える化B4・B5・B6系列の受領により5歳階級別の年齢調整を行った結果、所見7の結論（年齢構成を調整すると認定率は低下している）は裏付けられたが、65〜74歳は上昇しており「全年齢層で低下」は成り立たないこと、及び従来の説明「軽度は改善・中重度は悪化」が逆であることが判明した。後者は第10期の施策の重点を重度化防止から介護予防へ移す根拠となる。注4）残る未対応2件（No.12・No.15）は資料の受領を要する。確認事項No.7・No.11として依頼済みである。</t>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>訂正（指摘的中・追加）</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>No.27（地域差指数の分解）とNo.28（管内の位置）。いずれも見える化δ・D49・C1の受領により検証し、記述を訂正した</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="n"/>
+      <c r="E39" s="7" t="n"/>
+      <c r="F39" s="8" t="n"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>訂正（指摘的中）</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>No.5（3町の数値目標）とNo.1（年齢調整）。いずれも指摘が的中し、評価の記述を訂正した。特にNo.1では「軽度は改善・中重度は悪化」という従来の説明が逆であることが判明し、施策の重点に影響する</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="n"/>
+      <c r="E40" s="7" t="n"/>
+      <c r="F40" s="8" t="n"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>対応済（確認待ち）</t>
+        </is>
+      </c>
+      <c r="B41" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>No.4。注記済みで、条例による確認を依頼済み</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="n"/>
+      <c r="E41" s="7" t="n"/>
+      <c r="F41" s="8" t="n"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>未対応（資料待ち）</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>No.12・No.15。いずれも確認事項として依頼済み</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="n"/>
+      <c r="E42" s="7" t="n"/>
+      <c r="F42" s="8" t="n"/>
+    </row>
+    <row r="44" ht="108" customHeight="1">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>注1）No.5は本レビューの指摘が的中し、評価の結論そのものを訂正した事例である。「3町の高齢者福祉計画に数値目標が1件も設定されていない」という所見は誤りであり、東川町は令和6〜8年度を対象とする事業の数値目標を6事業10項目以上設定していた。検索語に依存した判定の危うさが実証された。注2）この訂正は第10期にとって前向きな材料でもある。東川町には事業の数値目標を年度別に設定し実績と対比する仕組みが既にあるため、第10期の共通指標の掲載は同町では実現可能性が高く、美瑛町・東神楽町にはその様式を参考として示すことができる。注3）No.1も指摘が的中した。見える化B4・B5・B6系列の受領により5歳階級別の年齢調整を行った結果、所見7の結論（年齢構成を調整すると認定率は低下している）は裏付けられたが、65〜74歳は上昇しており「全年齢層で低下」は成り立たないこと、及び従来の説明「軽度は改善・中重度は悪化」が逆であることが判明した。後者は第10期の施策の重点を重度化防止から介護予防へ移す根拠となる。注4）令和8年7月30日に見える化δ（自給率）・D49（地域差指数）・C1（保険料）を受領し、地域差の分析（15シート）を作成した。No.27（地域差指数の分解が恒等式として成り立たない）とNo.28（全国比のみで評価し管内の位置を見ていなかった）はいずれも指摘が的中し、記述を訂正した。特にNo.28では、給付水準の高さが平成21年度から続く構造であり、17年間の伸びは管内で小さい方（21保険者中16位）に属することが判明した。注5）残る未対応2件（No.12・No.15）は資料の受領を要する。確認事項No.7・No.11として依頼済みである。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="A44:F44"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A32:F32"/>
     <mergeCell ref="C38:F38"/>
-    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="C41:F41"/>
+    <mergeCell ref="C42:F42"/>
     <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C36:F36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_第9期評価のレッドチームレビュー.xlsx
+++ b/output/第10期計画_第9期評価のレッドチームレビュー.xlsx
@@ -4896,12 +4896,12 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>「分母の過大が原因」を「65歳以上人口がほぼ一致する一方で総人口が大きいため」に改める</t>
+          <t>「高齢者数が178人少ないことと総人口が382人多いことが重なるため」に改める（分子の寄与＋0.64pt＞分母＋0.46pt）</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>町別人口の実績（不足資料No.3）</t>
+          <t>―（見える化A系列により実施済）</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
@@ -5981,17 +5981,18 @@
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>対応中</t>
+          <t>訂正（指摘的中）</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>「65歳以上人口がほぼ一致する一方で総人口が大きいため」に改める。分母の差が生じた理由（基準差か社会増の見込みか）は町別人口の実績により検証する。</t>
+          <t>見える化A系列（人口・令和8年7月30日受領）により検証した。令和5年の高齢化率の差1.10ポイントを分解すると、分子（高齢者数が178人少ない）の寄与が＋0.64ポイント、分母（総人口が382人多い）の寄与が＋0.46ポイントであり、分子の寄与の方が大きい。「65歳以上人口はほぼ一致する」という前提も成り立たない（1.9％の差）。「高齢者数が178人少ないことと総人口が382人多いことが重なるため」に改めた。</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>妥当性検証 03シート</t>
+          <t>人口推計の基礎の検証 04シート
+妥当性検証 03シート</t>
         </is>
       </c>
     </row>
@@ -6229,11 +6230,11 @@
         </is>
       </c>
       <c r="B38" s="16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>No.19〜No.26及びNo.29。再レビューで新たに特定した指摘であり、改める記述を確定したうえで各成果物に反映する</t>
+          <t>No.19〜No.22・No.24〜No.26及びNo.29。再レビューで新たに特定した指摘であり、改める記述を確定したうえで各成果物に反映する</t>
         </is>
       </c>
       <c r="D38" s="7" t="n"/>
@@ -6247,11 +6248,11 @@
         </is>
       </c>
       <c r="B39" s="16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>No.27（地域差指数の分解）とNo.28（管内の位置）。いずれも見える化δ・D49・C1の受領により検証し、記述を訂正した</t>
+          <t>No.23（高齢化率の差の要因）・No.27（地域差指数の分解）・No.28（管内の位置）。いずれも見える化の系列を受領して検証し、記述を訂正した</t>
         </is>
       </c>
       <c r="D39" s="7" t="n"/>
@@ -6312,10 +6313,10 @@
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="8" t="n"/>
     </row>
-    <row r="44" ht="108" customHeight="1">
+    <row r="44" ht="132" customHeight="1">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>注1）No.5は本レビューの指摘が的中し、評価の結論そのものを訂正した事例である。「3町の高齢者福祉計画に数値目標が1件も設定されていない」という所見は誤りであり、東川町は令和6〜8年度を対象とする事業の数値目標を6事業10項目以上設定していた。検索語に依存した判定の危うさが実証された。注2）この訂正は第10期にとって前向きな材料でもある。東川町には事業の数値目標を年度別に設定し実績と対比する仕組みが既にあるため、第10期の共通指標の掲載は同町では実現可能性が高く、美瑛町・東神楽町にはその様式を参考として示すことができる。注3）No.1も指摘が的中した。見える化B4・B5・B6系列の受領により5歳階級別の年齢調整を行った結果、所見7の結論（年齢構成を調整すると認定率は低下している）は裏付けられたが、65〜74歳は上昇しており「全年齢層で低下」は成り立たないこと、及び従来の説明「軽度は改善・中重度は悪化」が逆であることが判明した。後者は第10期の施策の重点を重度化防止から介護予防へ移す根拠となる。注4）令和8年7月30日に見える化δ（自給率）・D49（地域差指数）・C1（保険料）を受領し、地域差の分析（15シート）を作成した。No.27（地域差指数の分解が恒等式として成り立たない）とNo.28（全国比のみで評価し管内の位置を見ていなかった）はいずれも指摘が的中し、記述を訂正した。特にNo.28では、給付水準の高さが平成21年度から続く構造であり、17年間の伸びは管内で小さい方（21保険者中16位）に属することが判明した。注5）残る未対応2件（No.12・No.15）は資料の受領を要する。確認事項No.7・No.11として依頼済みである。</t>
+          <t>注1）No.5は本レビューの指摘が的中し、評価の結論そのものを訂正した事例である。「3町の高齢者福祉計画に数値目標が1件も設定されていない」という所見は誤りであり、東川町は令和6〜8年度を対象とする事業の数値目標を6事業10項目以上設定していた。検索語に依存した判定の危うさが実証された。注2）この訂正は第10期にとって前向きな材料でもある。東川町には事業の数値目標を年度別に設定し実績と対比する仕組みが既にあるため、第10期の共通指標の掲載は同町では実現可能性が高く、美瑛町・東神楽町にはその様式を参考として示すことができる。注3）No.1も指摘が的中した。見える化B4・B5・B6系列の受領により5歳階級別の年齢調整を行った結果、所見7の結論（年齢構成を調整すると認定率は低下している）は裏付けられたが、65〜74歳は上昇しており「全年齢層で低下」は成り立たないこと、及び従来の説明「軽度は改善・中重度は悪化」が逆であることが判明した。後者は第10期の施策の重点を重度化防止から介護予防へ移す根拠となる。注4）令和8年7月30日に見える化δ（自給率）・D49（地域差指数）・C1（保険料）を受領し、地域差の分析（15シート）を作成した。No.27（地域差指数の分解が恒等式として成り立たない）とNo.28（全国比のみで評価し管内の位置を見ていなかった）はいずれも指摘が的中し、記述を訂正した。特にNo.28では、給付水準の高さが平成21年度から続く構造であり、17年間の伸びは管内で小さい方（21保険者中16位）に属することが判明した。注5）令和8年7月30日に見える化A系列（人口・2000〜2050年）を受領し、人口推計の基礎の検証（9シート）を作成した。No.23（高齢化率の差を「分母の過大が原因」とした）も指摘が的中し、分子（高齢者数）の寄与の方が大きいことが判明した。受託者の自己点検で指摘した箇所は、資料を得るとその多くで訂正が生じている。注6）残る未対応2件（No.12・No.15）は資料の受領を要する。確認事項No.7・No.11として依頼済みである。</t>
         </is>
       </c>
     </row>
